--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="802">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -1012,10 +1012,28 @@
     <t xml:space="preserve">into_darkness4</t>
   </si>
   <si>
-    <t xml:space="preserve">|It seems that you must throw some kind of liquid into the "Stagnation" at the farthest depth of the Crypt of the Damned. (to be continued)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|死者の洞窟の最奥にある「淀み」に、何らかの液体を投げ入れなければならないようだ。（続く）</t>
+    <t xml:space="preserve">|It seems that you must throw some kind of liquid into the "Stagnation" at the farthest depth of the Crypt of the Damned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|死者の洞窟の最奥にある「淀み」に、何らかの液体を投げ入れなければならないようだ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">into_darkness5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|Defeat Azrasizzle!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|アズラシズルを倒せ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">into_darkness6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|Your business in the Crypt of the Damned is done. Time to return to your base and await Issizzle's visit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|死者の洞窟での用は終わった。拠点でイスシズルからの報せを待とう。</t>
   </si>
   <si>
     <t xml:space="preserve">negotiation_darkness</t>
@@ -1072,10 +1090,10 @@
     <t xml:space="preserve">negotiation_darkness5</t>
   </si>
   <si>
-    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。</t>
+    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return. (To be continued)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。（続く）</t>
   </si>
   <si>
     <t xml:space="preserve">demitas_spellwriter</t>
@@ -2803,10 +2821,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C3" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -2815,7 +2833,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -2833,10 +2851,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C4" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2845,7 +2863,7 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -2863,12 +2881,12 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2886,10 +2904,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C6" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -2898,7 +2916,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -2916,10 +2934,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C7" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -2928,7 +2946,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="G7" t="s">
         <v>36</v>
@@ -2946,12 +2964,12 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="G8" t="s">
         <v>39</v>
@@ -2969,10 +2987,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -2981,7 +2999,7 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -2999,12 +3017,12 @@
         <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G10" t="s">
         <v>47</v>
@@ -3022,12 +3040,12 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="G11" t="s">
         <v>50</v>
@@ -3045,10 +3063,10 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C12" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3057,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="G12" t="s">
         <v>55</v>
@@ -3075,12 +3093,12 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -3098,10 +3116,10 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C14" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -3110,7 +3128,7 @@
         <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="G14" t="s">
         <v>63</v>
@@ -3121,7 +3139,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="M14" t="s">
         <v>65</v>
@@ -3135,10 +3153,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C15" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -3147,7 +3165,7 @@
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="G15" t="s">
         <v>70</v>
@@ -3172,10 +3190,10 @@
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C16" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -3184,7 +3202,7 @@
         <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
@@ -3202,10 +3220,10 @@
         <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C17" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D17" t="s">
         <v>80</v>
@@ -3214,7 +3232,7 @@
         <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="G17" t="s">
         <v>82</v>
@@ -3232,10 +3250,10 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C18" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
@@ -3244,7 +3262,7 @@
         <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G18" t="s">
         <v>87</v>
@@ -3262,10 +3280,10 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C19" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D19" t="s">
         <v>90</v>
@@ -3274,7 +3292,7 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
@@ -3290,12 +3308,12 @@
         <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
@@ -3311,7 +3329,7 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -3327,10 +3345,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C22" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -3339,7 +3357,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -3357,7 +3375,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -3373,10 +3391,10 @@
         <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C24" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D24" t="s">
         <v>103</v>
@@ -3385,7 +3403,7 @@
         <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -3403,12 +3421,12 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="G25" t="s">
         <v>108</v>
@@ -3426,12 +3444,12 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="G26" t="s">
         <v>111</v>
@@ -3449,7 +3467,7 @@
         <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -3465,10 +3483,10 @@
         <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C28" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -3477,7 +3495,7 @@
         <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="G28" t="s">
         <v>117</v>
@@ -3495,7 +3513,7 @@
         <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -3511,10 +3529,10 @@
         <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C30" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -3523,7 +3541,7 @@
         <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="G30" t="s">
         <v>82</v>
@@ -3541,10 +3559,10 @@
         <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C31" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -3553,7 +3571,7 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="G31" t="s">
         <v>82</v>
@@ -3571,10 +3589,10 @@
         <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C32" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D32" t="s">
         <v>128</v>
@@ -3583,7 +3601,7 @@
         <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="G32" t="s">
         <v>130</v>
@@ -3601,12 +3619,12 @@
         <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="G33" t="s">
         <v>133</v>
@@ -3624,7 +3642,7 @@
         <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D34"/>
       <c r="E34"/>
@@ -3640,10 +3658,10 @@
         <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C35" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D35" t="s">
         <v>137</v>
@@ -3652,7 +3670,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="G35" t="s">
         <v>139</v>
@@ -3670,12 +3688,12 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="G36" t="s">
         <v>142</v>
@@ -3693,12 +3711,12 @@
         <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="G37" t="s">
         <v>145</v>
@@ -3716,7 +3734,7 @@
         <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D38"/>
       <c r="E38"/>
@@ -3732,10 +3750,10 @@
         <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C39" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D39" t="s">
         <v>149</v>
@@ -3744,7 +3762,7 @@
         <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="G39" t="s">
         <v>151</v>
@@ -3762,12 +3780,12 @@
         <v>153</v>
       </c>
       <c r="B40" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="G40" t="s">
         <v>154</v>
@@ -3785,7 +3803,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D41"/>
       <c r="E41"/>
@@ -3801,10 +3819,10 @@
         <v>157</v>
       </c>
       <c r="B42" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C42" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D42" t="s">
         <v>158</v>
@@ -3813,7 +3831,7 @@
         <v>159</v>
       </c>
       <c r="F42" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="G42" t="s">
         <v>160</v>
@@ -3831,7 +3849,7 @@
         <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D43"/>
       <c r="E43"/>
@@ -3847,10 +3865,10 @@
         <v>163</v>
       </c>
       <c r="B44" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C44" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D44" t="s">
         <v>164</v>
@@ -3859,7 +3877,7 @@
         <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="G44" t="s">
         <v>166</v>
@@ -3877,12 +3895,12 @@
         <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="G45" t="s">
         <v>169</v>
@@ -3900,12 +3918,12 @@
         <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="G46" t="s">
         <v>172</v>
@@ -3923,12 +3941,12 @@
         <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="G47" t="s">
         <v>175</v>
@@ -3946,12 +3964,12 @@
         <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="G48" t="s">
         <v>175</v>
@@ -3969,12 +3987,12 @@
         <v>178</v>
       </c>
       <c r="B49" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
@@ -3992,7 +4010,7 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -4008,10 +4026,10 @@
         <v>182</v>
       </c>
       <c r="B51" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C51" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -4020,7 +4038,7 @@
         <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G51" t="s">
         <v>185</v>
@@ -4038,10 +4056,10 @@
         <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C52" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D52" t="s">
         <v>188</v>
@@ -4050,7 +4068,7 @@
         <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="G52" t="s">
         <v>190</v>
@@ -4068,7 +4086,7 @@
         <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D53"/>
       <c r="E53"/>
@@ -4084,10 +4102,10 @@
         <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C54" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
@@ -4096,7 +4114,7 @@
         <v>195</v>
       </c>
       <c r="F54" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="G54" t="s">
         <v>196</v>
@@ -4114,7 +4132,7 @@
         <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D55"/>
       <c r="E55"/>
@@ -4130,10 +4148,10 @@
         <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C56" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D56" t="s">
         <v>200</v>
@@ -4142,7 +4160,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -4160,10 +4178,10 @@
         <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C57" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D57" t="s">
         <v>205</v>
@@ -4172,7 +4190,7 @@
         <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="G57" t="s">
         <v>207</v>
@@ -4190,10 +4208,10 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C58" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D58" t="s">
         <v>210</v>
@@ -4202,7 +4220,7 @@
         <v>211</v>
       </c>
       <c r="F58" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="G58" t="s">
         <v>212</v>
@@ -4220,10 +4238,10 @@
         <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C59" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D59" t="s">
         <v>215</v>
@@ -4232,7 +4250,7 @@
         <v>216</v>
       </c>
       <c r="F59" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="G59" t="s">
         <v>217</v>
@@ -4250,10 +4268,10 @@
         <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C60" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D60" t="s">
         <v>220</v>
@@ -4262,7 +4280,7 @@
         <v>221</v>
       </c>
       <c r="F60" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G60" t="s">
         <v>222</v>
@@ -4280,10 +4298,10 @@
         <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C61" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D61" t="s">
         <v>225</v>
@@ -4292,7 +4310,7 @@
         <v>226</v>
       </c>
       <c r="F61" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G61" t="s">
         <v>227</v>
@@ -4310,10 +4328,10 @@
         <v>229</v>
       </c>
       <c r="B62" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C62" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D62" t="s">
         <v>230</v>
@@ -4322,7 +4340,7 @@
         <v>231</v>
       </c>
       <c r="F62" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="G62" t="s">
         <v>232</v>
@@ -4340,10 +4358,10 @@
         <v>234</v>
       </c>
       <c r="B63" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C63" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D63" t="s">
         <v>235</v>
@@ -4352,7 +4370,7 @@
         <v>236</v>
       </c>
       <c r="F63" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="G63" t="s">
         <v>237</v>
@@ -4370,12 +4388,12 @@
         <v>239</v>
       </c>
       <c r="B64" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D64"/>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="G64" t="s">
         <v>240</v>
@@ -4393,12 +4411,12 @@
         <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D65"/>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G65" t="s">
         <v>243</v>
@@ -4416,12 +4434,12 @@
         <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="D66"/>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="G66" t="s">
         <v>246</v>
@@ -4439,12 +4457,12 @@
         <v>248</v>
       </c>
       <c r="B67" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="G67" t="s">
         <v>249</v>
@@ -4462,12 +4480,12 @@
         <v>251</v>
       </c>
       <c r="B68" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="G68" t="s">
         <v>252</v>
@@ -4485,12 +4503,12 @@
         <v>254</v>
       </c>
       <c r="B69" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="G69" t="s">
         <v>255</v>
@@ -4508,12 +4526,12 @@
         <v>257</v>
       </c>
       <c r="B70" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="G70" t="s">
         <v>258</v>
@@ -4531,12 +4549,12 @@
         <v>260</v>
       </c>
       <c r="B71" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="G71" t="s">
         <v>261</v>
@@ -4554,12 +4572,12 @@
         <v>263</v>
       </c>
       <c r="B72" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="G72" t="s">
         <v>264</v>
@@ -4577,7 +4595,7 @@
         <v>266</v>
       </c>
       <c r="B73" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D73"/>
       <c r="E73"/>
@@ -4595,7 +4613,7 @@
         <v>268</v>
       </c>
       <c r="B74" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D74"/>
       <c r="E74"/>
@@ -4613,10 +4631,10 @@
         <v>269</v>
       </c>
       <c r="B75" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C75" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D75" t="s">
         <v>270</v>
@@ -4625,7 +4643,7 @@
         <v>271</v>
       </c>
       <c r="F75" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="G75" t="s">
         <v>272</v>
@@ -4643,10 +4661,10 @@
         <v>274</v>
       </c>
       <c r="B76" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C76" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D76" t="s">
         <v>275</v>
@@ -4655,7 +4673,7 @@
         <v>276</v>
       </c>
       <c r="F76" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="G76" t="s">
         <v>277</v>
@@ -4673,10 +4691,10 @@
         <v>279</v>
       </c>
       <c r="B77" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C77" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D77" t="s">
         <v>280</v>
@@ -4685,7 +4703,7 @@
         <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="G77" t="s">
         <v>282</v>
@@ -4703,10 +4721,10 @@
         <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C78" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D78" t="s">
         <v>285</v>
@@ -4715,7 +4733,7 @@
         <v>286</v>
       </c>
       <c r="F78" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="G78" t="s">
         <v>287</v>
@@ -4733,10 +4751,10 @@
         <v>289</v>
       </c>
       <c r="B79" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C79" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D79" t="s">
         <v>290</v>
@@ -4745,7 +4763,7 @@
         <v>291</v>
       </c>
       <c r="F79" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="G79" t="s">
         <v>292</v>
@@ -4763,7 +4781,7 @@
         <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D80"/>
       <c r="E80"/>
@@ -4784,10 +4802,10 @@
         <v>296</v>
       </c>
       <c r="B81" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C81" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D81" t="s">
         <v>297</v>
@@ -4796,7 +4814,7 @@
         <v>298</v>
       </c>
       <c r="F81" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="G81" t="s">
         <v>299</v>
@@ -4814,10 +4832,10 @@
         <v>301</v>
       </c>
       <c r="B82" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C82" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D82" t="s">
         <v>302</v>
@@ -4826,7 +4844,7 @@
         <v>303</v>
       </c>
       <c r="F82" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="G82" t="s">
         <v>304</v>
@@ -4844,10 +4862,10 @@
         <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C83" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D83" t="s">
         <v>307</v>
@@ -4856,7 +4874,7 @@
         <v>308</v>
       </c>
       <c r="F83" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="G83" t="s">
         <v>309</v>
@@ -4874,10 +4892,10 @@
         <v>311</v>
       </c>
       <c r="B84" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C84" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D84" t="s">
         <v>312</v>
@@ -4886,7 +4904,7 @@
         <v>313</v>
       </c>
       <c r="F84" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="G84" t="s">
         <v>232</v>
@@ -4904,10 +4922,10 @@
         <v>314</v>
       </c>
       <c r="B85" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C85" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D85" t="s">
         <v>315</v>
@@ -4916,7 +4934,7 @@
         <v>316</v>
       </c>
       <c r="F85" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="G85" t="s">
         <v>317</v>
@@ -4934,10 +4952,10 @@
         <v>319</v>
       </c>
       <c r="B86" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C86" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D86" t="s">
         <v>320</v>
@@ -4946,7 +4964,7 @@
         <v>321</v>
       </c>
       <c r="F86" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="G86" t="s">
         <v>322</v>
@@ -4964,12 +4982,12 @@
         <v>324</v>
       </c>
       <c r="B87" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G87" t="s">
         <v>325</v>
@@ -4987,12 +5005,12 @@
         <v>327</v>
       </c>
       <c r="B88" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G88" t="s">
         <v>325</v>
@@ -5010,12 +5028,12 @@
         <v>328</v>
       </c>
       <c r="B89" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="G89" t="s">
         <v>325</v>
@@ -5033,12 +5051,12 @@
         <v>329</v>
       </c>
       <c r="B90" t="s">
-        <v>584</v>
+        <v>15</v>
       </c>
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="G90" t="s">
         <v>330</v>
@@ -5056,25 +5074,15 @@
         <v>332</v>
       </c>
       <c r="B91" t="s">
-        <v>585</v>
-      </c>
-      <c r="C91" t="s">
-        <v>638</v>
-      </c>
-      <c r="D91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="G91" t="s">
         <v>333</v>
       </c>
-      <c r="E91" t="s">
+      <c r="H91" t="s">
         <v>334</v>
-      </c>
-      <c r="F91" t="s">
-        <v>749</v>
-      </c>
-      <c r="G91" t="s">
-        <v>335</v>
-      </c>
-      <c r="H91" t="s">
-        <v>336</v>
       </c>
       <c r="J91"/>
       <c r="K91"/>
@@ -5083,21 +5091,18 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B92" t="s">
-        <v>586</v>
+        <v>15</v>
       </c>
       <c r="D92"/>
       <c r="E92"/>
-      <c r="F92" t="s">
-        <v>750</v>
-      </c>
       <c r="G92" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H92" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J92"/>
       <c r="K92"/>
@@ -5106,15 +5111,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>338</v>
+      </c>
+      <c r="B93" t="s">
+        <v>591</v>
+      </c>
+      <c r="C93" t="s">
+        <v>644</v>
+      </c>
+      <c r="D93" t="s">
+        <v>339</v>
+      </c>
+      <c r="E93" t="s">
         <v>340</v>
       </c>
-      <c r="B93" t="s">
-        <v>586</v>
-      </c>
-      <c r="D93"/>
-      <c r="E93"/>
       <c r="F93" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="G93" t="s">
         <v>341</v>
@@ -5132,12 +5144,12 @@
         <v>343</v>
       </c>
       <c r="B94" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D94"/>
       <c r="E94"/>
       <c r="F94" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="G94" t="s">
         <v>344</v>
@@ -5155,12 +5167,12 @@
         <v>346</v>
       </c>
       <c r="B95" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G95" t="s">
         <v>347</v>
@@ -5178,12 +5190,12 @@
         <v>349</v>
       </c>
       <c r="B96" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G96" t="s">
         <v>350</v>
@@ -5201,25 +5213,18 @@
         <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>577</v>
-      </c>
-      <c r="C97" t="s">
-        <v>639</v>
-      </c>
-      <c r="D97" t="s">
+        <v>592</v>
+      </c>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97" t="s">
+        <v>759</v>
+      </c>
+      <c r="G97" t="s">
         <v>353</v>
       </c>
-      <c r="E97" t="s">
+      <c r="H97" t="s">
         <v>354</v>
-      </c>
-      <c r="F97" t="s">
-        <v>755</v>
-      </c>
-      <c r="G97" t="s">
-        <v>355</v>
-      </c>
-      <c r="H97" t="s">
-        <v>356</v>
       </c>
       <c r="J97"/>
       <c r="K97"/>
@@ -5228,28 +5233,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>355</v>
+      </c>
+      <c r="B98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98" t="s">
+        <v>760</v>
+      </c>
+      <c r="G98" t="s">
+        <v>356</v>
+      </c>
+      <c r="H98" t="s">
         <v>357</v>
-      </c>
-      <c r="B98" t="s">
-        <v>574</v>
-      </c>
-      <c r="C98" t="s">
-        <v>640</v>
-      </c>
-      <c r="D98" t="s">
-        <v>358</v>
-      </c>
-      <c r="E98" t="s">
-        <v>359</v>
-      </c>
-      <c r="F98" t="s">
-        <v>738</v>
-      </c>
-      <c r="G98" t="s">
-        <v>277</v>
-      </c>
-      <c r="H98" t="s">
-        <v>278</v>
       </c>
       <c r="J98"/>
       <c r="K98"/>
@@ -5258,28 +5256,28 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>358</v>
+      </c>
+      <c r="B99" t="s">
+        <v>583</v>
+      </c>
+      <c r="C99" t="s">
+        <v>645</v>
+      </c>
+      <c r="D99" t="s">
+        <v>359</v>
+      </c>
+      <c r="E99" t="s">
         <v>360</v>
       </c>
-      <c r="B99" t="s">
-        <v>574</v>
-      </c>
-      <c r="C99" t="s">
-        <v>640</v>
-      </c>
-      <c r="D99" t="s">
-        <v>358</v>
-      </c>
-      <c r="E99" t="s">
-        <v>359</v>
-      </c>
       <c r="F99" t="s">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="G99" t="s">
-        <v>277</v>
+        <v>361</v>
       </c>
       <c r="H99" t="s">
-        <v>278</v>
+        <v>362</v>
       </c>
       <c r="J99"/>
       <c r="K99"/>
@@ -5288,26 +5286,28 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B100" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C100" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F100" t="s">
-        <v>756</v>
-      </c>
-      <c r="G100"/>
+        <v>744</v>
+      </c>
+      <c r="G100" t="s">
+        <v>277</v>
+      </c>
       <c r="H100" t="s">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="J100"/>
       <c r="K100"/>
@@ -5316,22 +5316,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>366</v>
+      </c>
+      <c r="B101" t="s">
+        <v>580</v>
+      </c>
+      <c r="C101" t="s">
+        <v>646</v>
+      </c>
+      <c r="D101" t="s">
+        <v>364</v>
+      </c>
+      <c r="E101" t="s">
         <v>365</v>
       </c>
-      <c r="B101" t="s">
-        <v>587</v>
-      </c>
-      <c r="C101" t="s">
-        <v>642</v>
-      </c>
-      <c r="D101" t="s">
-        <v>366</v>
-      </c>
-      <c r="E101" t="s">
-        <v>367</v>
-      </c>
       <c r="F101" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="G101" t="s">
         <v>277</v>
@@ -5346,28 +5346,26 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>367</v>
+      </c>
+      <c r="B102" t="s">
+        <v>580</v>
+      </c>
+      <c r="C102" t="s">
+        <v>647</v>
+      </c>
+      <c r="D102" t="s">
         <v>368</v>
       </c>
-      <c r="B102" t="s">
-        <v>588</v>
-      </c>
-      <c r="C102" t="s">
-        <v>643</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>369</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>762</v>
+      </c>
+      <c r="G102"/>
+      <c r="H102" t="s">
         <v>370</v>
-      </c>
-      <c r="F102" t="s">
-        <v>371</v>
-      </c>
-      <c r="G102" t="s">
-        <v>371</v>
-      </c>
-      <c r="H102" t="s">
-        <v>371</v>
       </c>
       <c r="J102"/>
       <c r="K102"/>
@@ -5376,28 +5374,28 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
+        <v>371</v>
+      </c>
+      <c r="B103" t="s">
+        <v>593</v>
+      </c>
+      <c r="C103" t="s">
+        <v>648</v>
+      </c>
+      <c r="D103" t="s">
         <v>372</v>
       </c>
-      <c r="B103" t="s">
-        <v>588</v>
-      </c>
-      <c r="C103" t="s">
-        <v>644</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>373</v>
       </c>
-      <c r="E103" t="s">
-        <v>374</v>
-      </c>
       <c r="F103" t="s">
-        <v>371</v>
+        <v>744</v>
       </c>
       <c r="G103" t="s">
-        <v>371</v>
+        <v>277</v>
       </c>
       <c r="H103" t="s">
-        <v>371</v>
+        <v>278</v>
       </c>
       <c r="J103"/>
       <c r="K103"/>
@@ -5406,28 +5404,28 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>374</v>
+      </c>
+      <c r="B104" t="s">
+        <v>594</v>
+      </c>
+      <c r="C104" t="s">
+        <v>649</v>
+      </c>
+      <c r="D104" t="s">
         <v>375</v>
       </c>
-      <c r="B104" t="s">
-        <v>588</v>
-      </c>
-      <c r="C104" t="s">
-        <v>645</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>376</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>377</v>
       </c>
-      <c r="F104" t="s">
-        <v>371</v>
-      </c>
       <c r="G104" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H104" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="J104"/>
       <c r="K104"/>
@@ -5439,10 +5437,10 @@
         <v>378</v>
       </c>
       <c r="B105" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C105" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D105" t="s">
         <v>379</v>
@@ -5451,13 +5449,13 @@
         <v>380</v>
       </c>
       <c r="F105" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="G105" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H105" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="J105"/>
       <c r="K105"/>
@@ -5469,10 +5467,10 @@
         <v>381</v>
       </c>
       <c r="B106" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="C106" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D106" t="s">
         <v>382</v>
@@ -5481,13 +5479,13 @@
         <v>383</v>
       </c>
       <c r="F106" t="s">
-        <v>757</v>
+        <v>377</v>
       </c>
       <c r="G106" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="H106" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="J106"/>
       <c r="K106"/>
@@ -5496,21 +5494,28 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>384</v>
+      </c>
+      <c r="B107" t="s">
+        <v>594</v>
+      </c>
+      <c r="C107" t="s">
+        <v>652</v>
+      </c>
+      <c r="D107" t="s">
+        <v>385</v>
+      </c>
+      <c r="E107" t="s">
         <v>386</v>
       </c>
-      <c r="B107" t="s">
-        <v>565</v>
-      </c>
-      <c r="D107"/>
-      <c r="E107"/>
       <c r="F107" t="s">
-        <v>758</v>
+        <v>377</v>
       </c>
       <c r="G107" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="H107" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J107"/>
       <c r="K107"/>
@@ -5519,28 +5524,28 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>387</v>
+      </c>
+      <c r="B108" t="s">
+        <v>571</v>
+      </c>
+      <c r="C108" t="s">
+        <v>653</v>
+      </c>
+      <c r="D108" t="s">
+        <v>388</v>
+      </c>
+      <c r="E108" t="s">
         <v>389</v>
       </c>
-      <c r="B108" t="s">
-        <v>574</v>
-      </c>
-      <c r="C108" t="s">
-        <v>648</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
+        <v>763</v>
+      </c>
+      <c r="G108" t="s">
         <v>390</v>
       </c>
-      <c r="E108" t="s">
+      <c r="H108" t="s">
         <v>391</v>
-      </c>
-      <c r="F108" t="s">
-        <v>759</v>
-      </c>
-      <c r="G108" t="s">
-        <v>392</v>
-      </c>
-      <c r="H108" t="s">
-        <v>393</v>
       </c>
       <c r="J108"/>
       <c r="K108"/>
@@ -5549,28 +5554,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>392</v>
+      </c>
+      <c r="B109" t="s">
+        <v>571</v>
+      </c>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109" t="s">
+        <v>764</v>
+      </c>
+      <c r="G109" t="s">
+        <v>393</v>
+      </c>
+      <c r="H109" t="s">
         <v>394</v>
-      </c>
-      <c r="B109" t="s">
-        <v>565</v>
-      </c>
-      <c r="C109" t="s">
-        <v>649</v>
-      </c>
-      <c r="D109" t="s">
-        <v>395</v>
-      </c>
-      <c r="E109" t="s">
-        <v>396</v>
-      </c>
-      <c r="F109" t="s">
-        <v>760</v>
-      </c>
-      <c r="G109" t="s">
-        <v>397</v>
-      </c>
-      <c r="H109" t="s">
-        <v>398</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
@@ -5579,21 +5577,28 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>395</v>
+      </c>
+      <c r="B110" t="s">
+        <v>580</v>
+      </c>
+      <c r="C110" t="s">
+        <v>654</v>
+      </c>
+      <c r="D110" t="s">
+        <v>396</v>
+      </c>
+      <c r="E110" t="s">
+        <v>397</v>
+      </c>
+      <c r="F110" t="s">
+        <v>765</v>
+      </c>
+      <c r="G110" t="s">
+        <v>398</v>
+      </c>
+      <c r="H110" t="s">
         <v>399</v>
-      </c>
-      <c r="B110" t="s">
-        <v>565</v>
-      </c>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110" t="s">
-        <v>761</v>
-      </c>
-      <c r="G110" t="s">
-        <v>400</v>
-      </c>
-      <c r="H110" t="s">
-        <v>401</v>
       </c>
       <c r="J110"/>
       <c r="K110"/>
@@ -5602,28 +5607,28 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>400</v>
+      </c>
+      <c r="B111" t="s">
+        <v>571</v>
+      </c>
+      <c r="C111" t="s">
+        <v>655</v>
+      </c>
+      <c r="D111" t="s">
+        <v>401</v>
+      </c>
+      <c r="E111" t="s">
         <v>402</v>
       </c>
-      <c r="B111" t="s">
-        <v>574</v>
-      </c>
-      <c r="C111" t="s">
-        <v>650</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>766</v>
+      </c>
+      <c r="G111" t="s">
         <v>403</v>
       </c>
-      <c r="E111" t="s">
+      <c r="H111" t="s">
         <v>404</v>
-      </c>
-      <c r="F111" t="s">
-        <v>762</v>
-      </c>
-      <c r="G111" t="s">
-        <v>405</v>
-      </c>
-      <c r="H111" t="s">
-        <v>406</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
@@ -5632,28 +5637,21 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>405</v>
+      </c>
+      <c r="B112" t="s">
+        <v>571</v>
+      </c>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112" t="s">
+        <v>767</v>
+      </c>
+      <c r="G112" t="s">
+        <v>406</v>
+      </c>
+      <c r="H112" t="s">
         <v>407</v>
-      </c>
-      <c r="B112" t="s">
-        <v>565</v>
-      </c>
-      <c r="C112" t="s">
-        <v>651</v>
-      </c>
-      <c r="D112" t="s">
-        <v>408</v>
-      </c>
-      <c r="E112" t="s">
-        <v>409</v>
-      </c>
-      <c r="F112" t="s">
-        <v>763</v>
-      </c>
-      <c r="G112" t="s">
-        <v>410</v>
-      </c>
-      <c r="H112" t="s">
-        <v>411</v>
       </c>
       <c r="J112"/>
       <c r="K112"/>
@@ -5662,21 +5660,28 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>408</v>
+      </c>
+      <c r="B113" t="s">
+        <v>580</v>
+      </c>
+      <c r="C113" t="s">
+        <v>656</v>
+      </c>
+      <c r="D113" t="s">
+        <v>409</v>
+      </c>
+      <c r="E113" t="s">
+        <v>410</v>
+      </c>
+      <c r="F113" t="s">
+        <v>768</v>
+      </c>
+      <c r="G113" t="s">
+        <v>411</v>
+      </c>
+      <c r="H113" t="s">
         <v>412</v>
-      </c>
-      <c r="B113" t="s">
-        <v>565</v>
-      </c>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113" t="s">
-        <v>764</v>
-      </c>
-      <c r="G113" t="s">
-        <v>413</v>
-      </c>
-      <c r="H113" t="s">
-        <v>414</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
@@ -5685,28 +5690,28 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>413</v>
+      </c>
+      <c r="B114" t="s">
+        <v>571</v>
+      </c>
+      <c r="C114" t="s">
+        <v>657</v>
+      </c>
+      <c r="D114" t="s">
+        <v>414</v>
+      </c>
+      <c r="E114" t="s">
         <v>415</v>
       </c>
-      <c r="B114" t="s">
-        <v>574</v>
-      </c>
-      <c r="C114" t="s">
-        <v>652</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
+        <v>769</v>
+      </c>
+      <c r="G114" t="s">
         <v>416</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" t="s">
         <v>417</v>
-      </c>
-      <c r="F114" t="s">
-        <v>765</v>
-      </c>
-      <c r="G114" t="s">
-        <v>418</v>
-      </c>
-      <c r="H114" t="s">
-        <v>419</v>
       </c>
       <c r="J114"/>
       <c r="K114"/>
@@ -5715,28 +5720,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>418</v>
+      </c>
+      <c r="B115" t="s">
+        <v>571</v>
+      </c>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115" t="s">
+        <v>770</v>
+      </c>
+      <c r="G115" t="s">
+        <v>419</v>
+      </c>
+      <c r="H115" t="s">
         <v>420</v>
-      </c>
-      <c r="B115" t="s">
-        <v>589</v>
-      </c>
-      <c r="C115" t="s">
-        <v>653</v>
-      </c>
-      <c r="D115" t="s">
-        <v>421</v>
-      </c>
-      <c r="E115" t="s">
-        <v>422</v>
-      </c>
-      <c r="F115" t="s">
-        <v>766</v>
-      </c>
-      <c r="G115" t="s">
-        <v>423</v>
-      </c>
-      <c r="H115" t="s">
-        <v>424</v>
       </c>
       <c r="J115"/>
       <c r="K115"/>
@@ -5745,21 +5743,28 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>421</v>
+      </c>
+      <c r="B116" t="s">
+        <v>580</v>
+      </c>
+      <c r="C116" t="s">
+        <v>658</v>
+      </c>
+      <c r="D116" t="s">
+        <v>422</v>
+      </c>
+      <c r="E116" t="s">
+        <v>423</v>
+      </c>
+      <c r="F116" t="s">
+        <v>771</v>
+      </c>
+      <c r="G116" t="s">
+        <v>424</v>
+      </c>
+      <c r="H116" t="s">
         <v>425</v>
-      </c>
-      <c r="B116" t="s">
-        <v>590</v>
-      </c>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116" t="s">
-        <v>767</v>
-      </c>
-      <c r="G116" t="s">
-        <v>426</v>
-      </c>
-      <c r="H116" t="s">
-        <v>427</v>
       </c>
       <c r="J116"/>
       <c r="K116"/>
@@ -5768,28 +5773,28 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>426</v>
+      </c>
+      <c r="B117" t="s">
+        <v>595</v>
+      </c>
+      <c r="C117" t="s">
+        <v>659</v>
+      </c>
+      <c r="D117" t="s">
+        <v>427</v>
+      </c>
+      <c r="E117" t="s">
         <v>428</v>
       </c>
-      <c r="B117" t="s">
-        <v>574</v>
-      </c>
-      <c r="C117" t="s">
-        <v>654</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
+        <v>772</v>
+      </c>
+      <c r="G117" t="s">
         <v>429</v>
       </c>
-      <c r="E117" t="s">
+      <c r="H117" t="s">
         <v>430</v>
-      </c>
-      <c r="F117" t="s">
-        <v>768</v>
-      </c>
-      <c r="G117" t="s">
-        <v>431</v>
-      </c>
-      <c r="H117" t="s">
-        <v>432</v>
       </c>
       <c r="J117"/>
       <c r="K117"/>
@@ -5798,28 +5803,21 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
+        <v>431</v>
+      </c>
+      <c r="B118" t="s">
+        <v>596</v>
+      </c>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118" t="s">
+        <v>773</v>
+      </c>
+      <c r="G118" t="s">
+        <v>432</v>
+      </c>
+      <c r="H118" t="s">
         <v>433</v>
-      </c>
-      <c r="B118" t="s">
-        <v>574</v>
-      </c>
-      <c r="C118" t="s">
-        <v>655</v>
-      </c>
-      <c r="D118" t="s">
-        <v>434</v>
-      </c>
-      <c r="E118" t="s">
-        <v>435</v>
-      </c>
-      <c r="F118" t="s">
-        <v>769</v>
-      </c>
-      <c r="G118" t="s">
-        <v>436</v>
-      </c>
-      <c r="H118" t="s">
-        <v>437</v>
       </c>
       <c r="J118"/>
       <c r="K118"/>
@@ -5828,28 +5826,28 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>434</v>
+      </c>
+      <c r="B119" t="s">
+        <v>580</v>
+      </c>
+      <c r="C119" t="s">
+        <v>660</v>
+      </c>
+      <c r="D119" t="s">
+        <v>435</v>
+      </c>
+      <c r="E119" t="s">
+        <v>436</v>
+      </c>
+      <c r="F119" t="s">
+        <v>774</v>
+      </c>
+      <c r="G119" t="s">
+        <v>437</v>
+      </c>
+      <c r="H119" t="s">
         <v>438</v>
-      </c>
-      <c r="B119" t="s">
-        <v>578</v>
-      </c>
-      <c r="C119" t="s">
-        <v>656</v>
-      </c>
-      <c r="D119" t="s">
-        <v>439</v>
-      </c>
-      <c r="E119" t="s">
-        <v>440</v>
-      </c>
-      <c r="F119" t="s">
-        <v>770</v>
-      </c>
-      <c r="G119" t="s">
-        <v>441</v>
-      </c>
-      <c r="H119" t="s">
-        <v>442</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
@@ -5858,28 +5856,28 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>439</v>
+      </c>
+      <c r="B120" t="s">
+        <v>580</v>
+      </c>
+      <c r="C120" t="s">
+        <v>661</v>
+      </c>
+      <c r="D120" t="s">
+        <v>440</v>
+      </c>
+      <c r="E120" t="s">
+        <v>441</v>
+      </c>
+      <c r="F120" t="s">
+        <v>775</v>
+      </c>
+      <c r="G120" t="s">
+        <v>442</v>
+      </c>
+      <c r="H120" t="s">
         <v>443</v>
-      </c>
-      <c r="B120" t="s">
-        <v>574</v>
-      </c>
-      <c r="C120" t="s">
-        <v>657</v>
-      </c>
-      <c r="D120" t="s">
-        <v>444</v>
-      </c>
-      <c r="E120" t="s">
-        <v>445</v>
-      </c>
-      <c r="F120" t="s">
-        <v>771</v>
-      </c>
-      <c r="G120" t="s">
-        <v>446</v>
-      </c>
-      <c r="H120" t="s">
-        <v>447</v>
       </c>
       <c r="J120"/>
       <c r="K120"/>
@@ -5888,28 +5886,28 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>444</v>
+      </c>
+      <c r="B121" t="s">
+        <v>584</v>
+      </c>
+      <c r="C121" t="s">
+        <v>662</v>
+      </c>
+      <c r="D121" t="s">
+        <v>445</v>
+      </c>
+      <c r="E121" t="s">
+        <v>446</v>
+      </c>
+      <c r="F121" t="s">
+        <v>776</v>
+      </c>
+      <c r="G121" t="s">
+        <v>447</v>
+      </c>
+      <c r="H121" t="s">
         <v>448</v>
-      </c>
-      <c r="B121" t="s">
-        <v>574</v>
-      </c>
-      <c r="C121" t="s">
-        <v>658</v>
-      </c>
-      <c r="D121" t="s">
-        <v>449</v>
-      </c>
-      <c r="E121" t="s">
-        <v>450</v>
-      </c>
-      <c r="F121" t="s">
-        <v>772</v>
-      </c>
-      <c r="G121" t="s">
-        <v>451</v>
-      </c>
-      <c r="H121" t="s">
-        <v>452</v>
       </c>
       <c r="J121"/>
       <c r="K121"/>
@@ -5918,28 +5916,28 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>449</v>
+      </c>
+      <c r="B122" t="s">
+        <v>580</v>
+      </c>
+      <c r="C122" t="s">
+        <v>663</v>
+      </c>
+      <c r="D122" t="s">
+        <v>450</v>
+      </c>
+      <c r="E122" t="s">
+        <v>451</v>
+      </c>
+      <c r="F122" t="s">
+        <v>777</v>
+      </c>
+      <c r="G122" t="s">
+        <v>452</v>
+      </c>
+      <c r="H122" t="s">
         <v>453</v>
-      </c>
-      <c r="B122" t="s">
-        <v>591</v>
-      </c>
-      <c r="C122" t="s">
-        <v>659</v>
-      </c>
-      <c r="D122" t="s">
-        <v>454</v>
-      </c>
-      <c r="E122" t="s">
-        <v>455</v>
-      </c>
-      <c r="F122" t="s">
-        <v>773</v>
-      </c>
-      <c r="G122" t="s">
-        <v>456</v>
-      </c>
-      <c r="H122" t="s">
-        <v>457</v>
       </c>
       <c r="J122"/>
       <c r="K122"/>
@@ -5948,28 +5946,28 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>454</v>
+      </c>
+      <c r="B123" t="s">
+        <v>580</v>
+      </c>
+      <c r="C123" t="s">
+        <v>664</v>
+      </c>
+      <c r="D123" t="s">
+        <v>455</v>
+      </c>
+      <c r="E123" t="s">
+        <v>456</v>
+      </c>
+      <c r="F123" t="s">
+        <v>778</v>
+      </c>
+      <c r="G123" t="s">
+        <v>457</v>
+      </c>
+      <c r="H123" t="s">
         <v>458</v>
-      </c>
-      <c r="B123" t="s">
-        <v>592</v>
-      </c>
-      <c r="C123" t="s">
-        <v>660</v>
-      </c>
-      <c r="D123" t="s">
-        <v>459</v>
-      </c>
-      <c r="E123" t="s">
-        <v>460</v>
-      </c>
-      <c r="F123" t="s">
-        <v>774</v>
-      </c>
-      <c r="G123" t="s">
-        <v>461</v>
-      </c>
-      <c r="H123" t="s">
-        <v>462</v>
       </c>
       <c r="J123"/>
       <c r="K123"/>
@@ -5978,28 +5976,28 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>459</v>
+      </c>
+      <c r="B124" t="s">
+        <v>597</v>
+      </c>
+      <c r="C124" t="s">
+        <v>665</v>
+      </c>
+      <c r="D124" t="s">
+        <v>460</v>
+      </c>
+      <c r="E124" t="s">
+        <v>461</v>
+      </c>
+      <c r="F124" t="s">
+        <v>779</v>
+      </c>
+      <c r="G124" t="s">
+        <v>462</v>
+      </c>
+      <c r="H124" t="s">
         <v>463</v>
-      </c>
-      <c r="B124" t="s">
-        <v>574</v>
-      </c>
-      <c r="C124" t="s">
-        <v>661</v>
-      </c>
-      <c r="D124" t="s">
-        <v>464</v>
-      </c>
-      <c r="E124" t="s">
-        <v>465</v>
-      </c>
-      <c r="F124" t="s">
-        <v>775</v>
-      </c>
-      <c r="G124" t="s">
-        <v>466</v>
-      </c>
-      <c r="H124" t="s">
-        <v>467</v>
       </c>
       <c r="J124"/>
       <c r="K124"/>
@@ -6008,28 +6006,28 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>464</v>
+      </c>
+      <c r="B125" t="s">
+        <v>598</v>
+      </c>
+      <c r="C125" t="s">
+        <v>666</v>
+      </c>
+      <c r="D125" t="s">
+        <v>465</v>
+      </c>
+      <c r="E125" t="s">
+        <v>466</v>
+      </c>
+      <c r="F125" t="s">
+        <v>780</v>
+      </c>
+      <c r="G125" t="s">
+        <v>467</v>
+      </c>
+      <c r="H125" t="s">
         <v>468</v>
-      </c>
-      <c r="B125" t="s">
-        <v>574</v>
-      </c>
-      <c r="C125" t="s">
-        <v>662</v>
-      </c>
-      <c r="D125" t="s">
-        <v>469</v>
-      </c>
-      <c r="E125" t="s">
-        <v>470</v>
-      </c>
-      <c r="F125" t="s">
-        <v>776</v>
-      </c>
-      <c r="G125" t="s">
-        <v>471</v>
-      </c>
-      <c r="H125" t="s">
-        <v>472</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
@@ -6038,28 +6036,28 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>469</v>
+      </c>
+      <c r="B126" t="s">
+        <v>580</v>
+      </c>
+      <c r="C126" t="s">
+        <v>667</v>
+      </c>
+      <c r="D126" t="s">
+        <v>470</v>
+      </c>
+      <c r="E126" t="s">
+        <v>471</v>
+      </c>
+      <c r="F126" t="s">
+        <v>781</v>
+      </c>
+      <c r="G126" t="s">
+        <v>472</v>
+      </c>
+      <c r="H126" t="s">
         <v>473</v>
-      </c>
-      <c r="B126" t="s">
-        <v>574</v>
-      </c>
-      <c r="C126" t="s">
-        <v>663</v>
-      </c>
-      <c r="D126" t="s">
-        <v>474</v>
-      </c>
-      <c r="E126" t="s">
-        <v>475</v>
-      </c>
-      <c r="F126" t="s">
-        <v>777</v>
-      </c>
-      <c r="G126" t="s">
-        <v>476</v>
-      </c>
-      <c r="H126" t="s">
-        <v>477</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
@@ -6068,28 +6066,28 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>474</v>
+      </c>
+      <c r="B127" t="s">
+        <v>580</v>
+      </c>
+      <c r="C127" t="s">
+        <v>668</v>
+      </c>
+      <c r="D127" t="s">
+        <v>475</v>
+      </c>
+      <c r="E127" t="s">
+        <v>476</v>
+      </c>
+      <c r="F127" t="s">
+        <v>782</v>
+      </c>
+      <c r="G127" t="s">
+        <v>477</v>
+      </c>
+      <c r="H127" t="s">
         <v>478</v>
-      </c>
-      <c r="B127" t="s">
-        <v>574</v>
-      </c>
-      <c r="C127" t="s">
-        <v>664</v>
-      </c>
-      <c r="D127" t="s">
-        <v>479</v>
-      </c>
-      <c r="E127" t="s">
-        <v>480</v>
-      </c>
-      <c r="F127" t="s">
-        <v>778</v>
-      </c>
-      <c r="G127" t="s">
-        <v>481</v>
-      </c>
-      <c r="H127" t="s">
-        <v>482</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
@@ -6098,28 +6096,28 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>479</v>
+      </c>
+      <c r="B128" t="s">
+        <v>580</v>
+      </c>
+      <c r="C128" t="s">
+        <v>669</v>
+      </c>
+      <c r="D128" t="s">
+        <v>480</v>
+      </c>
+      <c r="E128" t="s">
+        <v>481</v>
+      </c>
+      <c r="F128" t="s">
+        <v>783</v>
+      </c>
+      <c r="G128" t="s">
+        <v>482</v>
+      </c>
+      <c r="H128" t="s">
         <v>483</v>
-      </c>
-      <c r="B128" t="s">
-        <v>577</v>
-      </c>
-      <c r="C128" t="s">
-        <v>665</v>
-      </c>
-      <c r="D128" t="s">
-        <v>484</v>
-      </c>
-      <c r="E128" t="s">
-        <v>485</v>
-      </c>
-      <c r="F128" t="s">
-        <v>779</v>
-      </c>
-      <c r="G128" t="s">
-        <v>486</v>
-      </c>
-      <c r="H128" t="s">
-        <v>487</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
@@ -6128,28 +6126,28 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>484</v>
+      </c>
+      <c r="B129" t="s">
+        <v>580</v>
+      </c>
+      <c r="C129" t="s">
+        <v>670</v>
+      </c>
+      <c r="D129" t="s">
+        <v>485</v>
+      </c>
+      <c r="E129" t="s">
+        <v>486</v>
+      </c>
+      <c r="F129" t="s">
+        <v>784</v>
+      </c>
+      <c r="G129" t="s">
+        <v>487</v>
+      </c>
+      <c r="H129" t="s">
         <v>488</v>
-      </c>
-      <c r="B129" t="s">
-        <v>574</v>
-      </c>
-      <c r="C129" t="s">
-        <v>666</v>
-      </c>
-      <c r="D129" t="s">
-        <v>489</v>
-      </c>
-      <c r="E129" t="s">
-        <v>490</v>
-      </c>
-      <c r="F129" t="s">
-        <v>780</v>
-      </c>
-      <c r="G129" t="s">
-        <v>491</v>
-      </c>
-      <c r="H129" t="s">
-        <v>492</v>
       </c>
       <c r="J129"/>
       <c r="K129"/>
@@ -6158,28 +6156,28 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>489</v>
+      </c>
+      <c r="B130" t="s">
+        <v>583</v>
+      </c>
+      <c r="C130" t="s">
+        <v>671</v>
+      </c>
+      <c r="D130" t="s">
+        <v>490</v>
+      </c>
+      <c r="E130" t="s">
+        <v>491</v>
+      </c>
+      <c r="F130" t="s">
+        <v>785</v>
+      </c>
+      <c r="G130" t="s">
+        <v>492</v>
+      </c>
+      <c r="H130" t="s">
         <v>493</v>
-      </c>
-      <c r="B130" t="s">
-        <v>574</v>
-      </c>
-      <c r="C130" t="s">
-        <v>667</v>
-      </c>
-      <c r="D130" t="s">
-        <v>494</v>
-      </c>
-      <c r="E130" t="s">
-        <v>495</v>
-      </c>
-      <c r="F130" t="s">
-        <v>781</v>
-      </c>
-      <c r="G130" t="s">
-        <v>496</v>
-      </c>
-      <c r="H130" t="s">
-        <v>497</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
@@ -6188,28 +6186,28 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>494</v>
+      </c>
+      <c r="B131" t="s">
+        <v>580</v>
+      </c>
+      <c r="C131" t="s">
+        <v>672</v>
+      </c>
+      <c r="D131" t="s">
+        <v>495</v>
+      </c>
+      <c r="E131" t="s">
+        <v>496</v>
+      </c>
+      <c r="F131" t="s">
+        <v>786</v>
+      </c>
+      <c r="G131" t="s">
+        <v>497</v>
+      </c>
+      <c r="H131" t="s">
         <v>498</v>
-      </c>
-      <c r="B131" t="s">
-        <v>574</v>
-      </c>
-      <c r="C131" t="s">
-        <v>668</v>
-      </c>
-      <c r="D131" t="s">
-        <v>499</v>
-      </c>
-      <c r="E131" t="s">
-        <v>500</v>
-      </c>
-      <c r="F131" t="s">
-        <v>782</v>
-      </c>
-      <c r="G131" t="s">
-        <v>501</v>
-      </c>
-      <c r="H131" t="s">
-        <v>502</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
@@ -6218,28 +6216,28 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
+        <v>499</v>
+      </c>
+      <c r="B132" t="s">
+        <v>580</v>
+      </c>
+      <c r="C132" t="s">
+        <v>673</v>
+      </c>
+      <c r="D132" t="s">
+        <v>500</v>
+      </c>
+      <c r="E132" t="s">
+        <v>501</v>
+      </c>
+      <c r="F132" t="s">
+        <v>787</v>
+      </c>
+      <c r="G132" t="s">
+        <v>502</v>
+      </c>
+      <c r="H132" t="s">
         <v>503</v>
-      </c>
-      <c r="B132" t="s">
-        <v>574</v>
-      </c>
-      <c r="C132" t="s">
-        <v>669</v>
-      </c>
-      <c r="D132" t="s">
-        <v>504</v>
-      </c>
-      <c r="E132" t="s">
-        <v>505</v>
-      </c>
-      <c r="F132" t="s">
-        <v>783</v>
-      </c>
-      <c r="G132" t="s">
-        <v>506</v>
-      </c>
-      <c r="H132" t="s">
-        <v>507</v>
       </c>
       <c r="J132"/>
       <c r="K132"/>
@@ -6248,28 +6246,28 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
+        <v>504</v>
+      </c>
+      <c r="B133" t="s">
+        <v>580</v>
+      </c>
+      <c r="C133" t="s">
+        <v>674</v>
+      </c>
+      <c r="D133" t="s">
+        <v>505</v>
+      </c>
+      <c r="E133" t="s">
+        <v>506</v>
+      </c>
+      <c r="F133" t="s">
+        <v>788</v>
+      </c>
+      <c r="G133" t="s">
+        <v>507</v>
+      </c>
+      <c r="H133" t="s">
         <v>508</v>
-      </c>
-      <c r="B133" t="s">
-        <v>574</v>
-      </c>
-      <c r="C133" t="s">
-        <v>670</v>
-      </c>
-      <c r="D133" t="s">
-        <v>509</v>
-      </c>
-      <c r="E133" t="s">
-        <v>510</v>
-      </c>
-      <c r="F133" t="s">
-        <v>784</v>
-      </c>
-      <c r="G133" t="s">
-        <v>511</v>
-      </c>
-      <c r="H133" t="s">
-        <v>512</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
@@ -6278,28 +6276,28 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
+        <v>509</v>
+      </c>
+      <c r="B134" t="s">
+        <v>580</v>
+      </c>
+      <c r="C134" t="s">
+        <v>675</v>
+      </c>
+      <c r="D134" t="s">
+        <v>510</v>
+      </c>
+      <c r="E134" t="s">
+        <v>511</v>
+      </c>
+      <c r="F134" t="s">
+        <v>789</v>
+      </c>
+      <c r="G134" t="s">
+        <v>512</v>
+      </c>
+      <c r="H134" t="s">
         <v>513</v>
-      </c>
-      <c r="B134" t="s">
-        <v>574</v>
-      </c>
-      <c r="C134" t="s">
-        <v>671</v>
-      </c>
-      <c r="D134" t="s">
-        <v>514</v>
-      </c>
-      <c r="E134" t="s">
-        <v>515</v>
-      </c>
-      <c r="F134" t="s">
-        <v>785</v>
-      </c>
-      <c r="G134" t="s">
-        <v>516</v>
-      </c>
-      <c r="H134" t="s">
-        <v>517</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
@@ -6308,28 +6306,28 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
+        <v>514</v>
+      </c>
+      <c r="B135" t="s">
+        <v>580</v>
+      </c>
+      <c r="C135" t="s">
+        <v>676</v>
+      </c>
+      <c r="D135" t="s">
+        <v>515</v>
+      </c>
+      <c r="E135" t="s">
+        <v>516</v>
+      </c>
+      <c r="F135" t="s">
+        <v>790</v>
+      </c>
+      <c r="G135" t="s">
+        <v>517</v>
+      </c>
+      <c r="H135" t="s">
         <v>518</v>
-      </c>
-      <c r="B135" t="s">
-        <v>574</v>
-      </c>
-      <c r="C135" t="s">
-        <v>672</v>
-      </c>
-      <c r="D135" t="s">
-        <v>519</v>
-      </c>
-      <c r="E135" t="s">
-        <v>520</v>
-      </c>
-      <c r="F135" t="s">
-        <v>786</v>
-      </c>
-      <c r="G135" t="s">
-        <v>521</v>
-      </c>
-      <c r="H135" t="s">
-        <v>522</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
@@ -6338,28 +6336,28 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>519</v>
+      </c>
+      <c r="B136" t="s">
+        <v>580</v>
+      </c>
+      <c r="C136" t="s">
+        <v>677</v>
+      </c>
+      <c r="D136" t="s">
+        <v>520</v>
+      </c>
+      <c r="E136" t="s">
+        <v>521</v>
+      </c>
+      <c r="F136" t="s">
+        <v>791</v>
+      </c>
+      <c r="G136" t="s">
+        <v>522</v>
+      </c>
+      <c r="H136" t="s">
         <v>523</v>
-      </c>
-      <c r="B136" t="s">
-        <v>574</v>
-      </c>
-      <c r="C136" t="s">
-        <v>672</v>
-      </c>
-      <c r="D136" t="s">
-        <v>519</v>
-      </c>
-      <c r="E136" t="s">
-        <v>520</v>
-      </c>
-      <c r="F136" t="s">
-        <v>786</v>
-      </c>
-      <c r="G136" t="s">
-        <v>521</v>
-      </c>
-      <c r="H136" t="s">
-        <v>524</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
@@ -6368,28 +6366,28 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>524</v>
+      </c>
+      <c r="B137" t="s">
+        <v>580</v>
+      </c>
+      <c r="C137" t="s">
+        <v>678</v>
+      </c>
+      <c r="D137" t="s">
         <v>525</v>
       </c>
-      <c r="B137" t="s">
-        <v>574</v>
-      </c>
-      <c r="C137" t="s">
-        <v>673</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>526</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
+        <v>792</v>
+      </c>
+      <c r="G137" t="s">
         <v>527</v>
       </c>
-      <c r="F137" t="s">
-        <v>787</v>
-      </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>528</v>
-      </c>
-      <c r="H137" t="s">
-        <v>529</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
@@ -6398,28 +6396,28 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>529</v>
+      </c>
+      <c r="B138" t="s">
+        <v>580</v>
+      </c>
+      <c r="C138" t="s">
+        <v>678</v>
+      </c>
+      <c r="D138" t="s">
+        <v>525</v>
+      </c>
+      <c r="E138" t="s">
+        <v>526</v>
+      </c>
+      <c r="F138" t="s">
+        <v>792</v>
+      </c>
+      <c r="G138" t="s">
+        <v>527</v>
+      </c>
+      <c r="H138" t="s">
         <v>530</v>
-      </c>
-      <c r="B138" t="s">
-        <v>574</v>
-      </c>
-      <c r="C138" t="s">
-        <v>674</v>
-      </c>
-      <c r="D138" t="s">
-        <v>531</v>
-      </c>
-      <c r="E138" t="s">
-        <v>532</v>
-      </c>
-      <c r="F138" t="s">
-        <v>788</v>
-      </c>
-      <c r="G138" t="s">
-        <v>533</v>
-      </c>
-      <c r="H138" t="s">
-        <v>534</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
@@ -6428,28 +6426,28 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
+        <v>531</v>
+      </c>
+      <c r="B139" t="s">
+        <v>580</v>
+      </c>
+      <c r="C139" t="s">
+        <v>679</v>
+      </c>
+      <c r="D139" t="s">
+        <v>532</v>
+      </c>
+      <c r="E139" t="s">
+        <v>533</v>
+      </c>
+      <c r="F139" t="s">
+        <v>793</v>
+      </c>
+      <c r="G139" t="s">
+        <v>534</v>
+      </c>
+      <c r="H139" t="s">
         <v>535</v>
-      </c>
-      <c r="B139" t="s">
-        <v>574</v>
-      </c>
-      <c r="C139" t="s">
-        <v>675</v>
-      </c>
-      <c r="D139" t="s">
-        <v>536</v>
-      </c>
-      <c r="E139" t="s">
-        <v>537</v>
-      </c>
-      <c r="F139" t="s">
-        <v>789</v>
-      </c>
-      <c r="G139" t="s">
-        <v>538</v>
-      </c>
-      <c r="H139" t="s">
-        <v>539</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
@@ -6458,28 +6456,28 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>536</v>
+      </c>
+      <c r="B140" t="s">
+        <v>580</v>
+      </c>
+      <c r="C140" t="s">
+        <v>680</v>
+      </c>
+      <c r="D140" t="s">
+        <v>537</v>
+      </c>
+      <c r="E140" t="s">
+        <v>538</v>
+      </c>
+      <c r="F140" t="s">
+        <v>794</v>
+      </c>
+      <c r="G140" t="s">
+        <v>539</v>
+      </c>
+      <c r="H140" t="s">
         <v>540</v>
-      </c>
-      <c r="B140" t="s">
-        <v>574</v>
-      </c>
-      <c r="C140" t="s">
-        <v>676</v>
-      </c>
-      <c r="D140" t="s">
-        <v>541</v>
-      </c>
-      <c r="E140" t="s">
-        <v>542</v>
-      </c>
-      <c r="F140" t="s">
-        <v>790</v>
-      </c>
-      <c r="G140" t="s">
-        <v>543</v>
-      </c>
-      <c r="H140" t="s">
-        <v>544</v>
       </c>
       <c r="J140"/>
       <c r="K140"/>
@@ -6488,28 +6486,28 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>541</v>
+      </c>
+      <c r="B141" t="s">
+        <v>580</v>
+      </c>
+      <c r="C141" t="s">
+        <v>681</v>
+      </c>
+      <c r="D141" t="s">
+        <v>542</v>
+      </c>
+      <c r="E141" t="s">
+        <v>543</v>
+      </c>
+      <c r="F141" t="s">
+        <v>795</v>
+      </c>
+      <c r="G141" t="s">
+        <v>544</v>
+      </c>
+      <c r="H141" t="s">
         <v>545</v>
-      </c>
-      <c r="B141" t="s">
-        <v>574</v>
-      </c>
-      <c r="C141" t="s">
-        <v>677</v>
-      </c>
-      <c r="D141" t="s">
-        <v>546</v>
-      </c>
-      <c r="E141" t="s">
-        <v>547</v>
-      </c>
-      <c r="F141" t="s">
-        <v>791</v>
-      </c>
-      <c r="G141" t="s">
-        <v>548</v>
-      </c>
-      <c r="H141" t="s">
-        <v>549</v>
       </c>
       <c r="J141"/>
       <c r="K141"/>
@@ -6518,28 +6516,28 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
+        <v>546</v>
+      </c>
+      <c r="B142" t="s">
+        <v>580</v>
+      </c>
+      <c r="C142" t="s">
+        <v>682</v>
+      </c>
+      <c r="D142" t="s">
+        <v>547</v>
+      </c>
+      <c r="E142" t="s">
+        <v>548</v>
+      </c>
+      <c r="F142" t="s">
+        <v>796</v>
+      </c>
+      <c r="G142" t="s">
+        <v>549</v>
+      </c>
+      <c r="H142" t="s">
         <v>550</v>
-      </c>
-      <c r="B142" t="s">
-        <v>593</v>
-      </c>
-      <c r="C142" t="s">
-        <v>678</v>
-      </c>
-      <c r="D142" t="s">
-        <v>551</v>
-      </c>
-      <c r="E142" t="s">
-        <v>552</v>
-      </c>
-      <c r="F142" t="s">
-        <v>792</v>
-      </c>
-      <c r="G142" t="s">
-        <v>553</v>
-      </c>
-      <c r="H142" t="s">
-        <v>554</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
@@ -6548,28 +6546,28 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>551</v>
+      </c>
+      <c r="B143" t="s">
+        <v>580</v>
+      </c>
+      <c r="C143" t="s">
+        <v>683</v>
+      </c>
+      <c r="D143" t="s">
+        <v>552</v>
+      </c>
+      <c r="E143" t="s">
+        <v>553</v>
+      </c>
+      <c r="F143" t="s">
+        <v>797</v>
+      </c>
+      <c r="G143" t="s">
+        <v>554</v>
+      </c>
+      <c r="H143" t="s">
         <v>555</v>
-      </c>
-      <c r="B143" t="s">
-        <v>578</v>
-      </c>
-      <c r="C143" t="s">
-        <v>679</v>
-      </c>
-      <c r="D143" t="s">
-        <v>556</v>
-      </c>
-      <c r="E143" t="s">
-        <v>557</v>
-      </c>
-      <c r="F143" t="s">
-        <v>793</v>
-      </c>
-      <c r="G143" t="s">
-        <v>558</v>
-      </c>
-      <c r="H143" t="s">
-        <v>559</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
@@ -6578,33 +6576,93 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
+        <v>556</v>
+      </c>
+      <c r="B144" t="s">
+        <v>599</v>
+      </c>
+      <c r="C144" t="s">
+        <v>684</v>
+      </c>
+      <c r="D144" t="s">
+        <v>557</v>
+      </c>
+      <c r="E144" t="s">
+        <v>558</v>
+      </c>
+      <c r="F144" t="s">
+        <v>798</v>
+      </c>
+      <c r="G144" t="s">
+        <v>559</v>
+      </c>
+      <c r="H144" t="s">
         <v>560</v>
-      </c>
-      <c r="B144" t="s">
-        <v>578</v>
-      </c>
-      <c r="C144" t="s">
-        <v>680</v>
-      </c>
-      <c r="D144" t="s">
-        <v>561</v>
-      </c>
-      <c r="E144" t="s">
-        <v>562</v>
-      </c>
-      <c r="F144" t="s">
-        <v>794</v>
-      </c>
-      <c r="G144" t="s">
-        <v>563</v>
-      </c>
-      <c r="H144" t="s">
-        <v>564</v>
       </c>
       <c r="J144"/>
       <c r="K144"/>
       <c r="M144"/>
       <c r="N144"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>561</v>
+      </c>
+      <c r="B145" t="s">
+        <v>584</v>
+      </c>
+      <c r="C145" t="s">
+        <v>685</v>
+      </c>
+      <c r="D145" t="s">
+        <v>562</v>
+      </c>
+      <c r="E145" t="s">
+        <v>563</v>
+      </c>
+      <c r="F145" t="s">
+        <v>799</v>
+      </c>
+      <c r="G145" t="s">
+        <v>564</v>
+      </c>
+      <c r="H145" t="s">
+        <v>565</v>
+      </c>
+      <c r="J145"/>
+      <c r="K145"/>
+      <c r="M145"/>
+      <c r="N145"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>566</v>
+      </c>
+      <c r="B146" t="s">
+        <v>584</v>
+      </c>
+      <c r="C146" t="s">
+        <v>686</v>
+      </c>
+      <c r="D146" t="s">
+        <v>567</v>
+      </c>
+      <c r="E146" t="s">
+        <v>568</v>
+      </c>
+      <c r="F146" t="s">
+        <v>800</v>
+      </c>
+      <c r="G146" t="s">
+        <v>569</v>
+      </c>
+      <c r="H146" t="s">
+        <v>570</v>
+      </c>
+      <c r="J146"/>
+      <c r="K146"/>
+      <c r="M146"/>
+      <c r="N146"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:N2"/>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="815">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -1099,10 +1099,10 @@
     <t xml:space="preserve">negotiation_darkness5</t>
   </si>
   <si>
-    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return. (To be continued)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。（続く）</t>
+    <t xml:space="preserve">|You have finished your business in the Village of Atonement. Let's wait for Kettle to return.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|贖罪の村での用事を終えた。ケトルの帰りを待とう。</t>
   </si>
   <si>
     <t xml:space="preserve">demitas_spellwriter</t>
@@ -1915,6 +1915,21 @@
   </si>
   <si>
     <t xml:space="preserve">クラフト素材のトラック。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding Ceremony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結婚式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I love you. Let’s cerebrate with an unforgettable wedding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好き{だ}。素晴らしい式をあげる{のだ}。</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -2845,10 +2860,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C3" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -2857,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -2875,10 +2890,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2887,7 +2902,7 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -2905,12 +2920,12 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2928,10 +2943,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C6" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -2940,7 +2955,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -2958,10 +2973,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C7" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -2970,7 +2985,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G7" t="s">
         <v>36</v>
@@ -2988,12 +3003,12 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="G8" t="s">
         <v>39</v>
@@ -3011,10 +3026,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C9" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -3023,7 +3038,7 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -3041,12 +3056,12 @@
         <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="G10" t="s">
         <v>47</v>
@@ -3064,12 +3079,12 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G11" t="s">
         <v>50</v>
@@ -3087,10 +3102,10 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C12" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3099,7 +3114,7 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G12" t="s">
         <v>55</v>
@@ -3117,12 +3132,12 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -3140,10 +3155,10 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C14" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -3152,7 +3167,7 @@
         <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G14" t="s">
         <v>63</v>
@@ -3163,7 +3178,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="M14" t="s">
         <v>65</v>
@@ -3177,10 +3192,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C15" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -3189,7 +3204,7 @@
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="G15" t="s">
         <v>70</v>
@@ -3214,10 +3229,10 @@
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C16" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -3226,7 +3241,7 @@
         <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
@@ -3244,10 +3259,10 @@
         <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C17" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D17" t="s">
         <v>80</v>
@@ -3256,7 +3271,7 @@
         <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G17" t="s">
         <v>82</v>
@@ -3274,10 +3289,10 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C18" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
@@ -3286,7 +3301,7 @@
         <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="G18" t="s">
         <v>87</v>
@@ -3304,10 +3319,10 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C19" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D19" t="s">
         <v>90</v>
@@ -3316,7 +3331,7 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
@@ -3332,12 +3347,12 @@
         <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
@@ -3353,7 +3368,7 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -3369,10 +3384,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C22" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -3381,7 +3396,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -3399,7 +3414,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -3415,10 +3430,10 @@
         <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C24" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D24" t="s">
         <v>103</v>
@@ -3427,7 +3442,7 @@
         <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -3445,12 +3460,12 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G25" t="s">
         <v>108</v>
@@ -3468,12 +3483,12 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G26" t="s">
         <v>111</v>
@@ -3491,7 +3506,7 @@
         <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -3507,10 +3522,10 @@
         <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C28" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -3519,7 +3534,7 @@
         <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="G28" t="s">
         <v>117</v>
@@ -3537,7 +3552,7 @@
         <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -3553,10 +3568,10 @@
         <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C30" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -3565,7 +3580,7 @@
         <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G30" t="s">
         <v>82</v>
@@ -3583,10 +3598,10 @@
         <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C31" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -3595,7 +3610,7 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G31" t="s">
         <v>82</v>
@@ -3613,10 +3628,10 @@
         <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C32" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D32" t="s">
         <v>128</v>
@@ -3625,7 +3640,7 @@
         <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G32" t="s">
         <v>130</v>
@@ -3643,12 +3658,12 @@
         <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="G33" t="s">
         <v>133</v>
@@ -3666,7 +3681,7 @@
         <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D34"/>
       <c r="E34"/>
@@ -3682,10 +3697,10 @@
         <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C35" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D35" t="s">
         <v>137</v>
@@ -3694,7 +3709,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="G35" t="s">
         <v>139</v>
@@ -3712,12 +3727,12 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="G36" t="s">
         <v>142</v>
@@ -3735,12 +3750,12 @@
         <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="G37" t="s">
         <v>145</v>
@@ -3758,7 +3773,7 @@
         <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D38"/>
       <c r="E38"/>
@@ -3774,10 +3789,10 @@
         <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C39" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D39" t="s">
         <v>149</v>
@@ -3786,7 +3801,7 @@
         <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G39" t="s">
         <v>151</v>
@@ -3804,12 +3819,12 @@
         <v>153</v>
       </c>
       <c r="B40" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="G40" t="s">
         <v>154</v>
@@ -3827,7 +3842,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D41"/>
       <c r="E41"/>
@@ -3843,10 +3858,10 @@
         <v>157</v>
       </c>
       <c r="B42" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C42" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D42" t="s">
         <v>158</v>
@@ -3855,7 +3870,7 @@
         <v>159</v>
       </c>
       <c r="F42" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="G42" t="s">
         <v>160</v>
@@ -3873,7 +3888,7 @@
         <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D43"/>
       <c r="E43"/>
@@ -3889,10 +3904,10 @@
         <v>163</v>
       </c>
       <c r="B44" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C44" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D44" t="s">
         <v>164</v>
@@ -3901,7 +3916,7 @@
         <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="G44" t="s">
         <v>166</v>
@@ -3919,12 +3934,12 @@
         <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="G45" t="s">
         <v>169</v>
@@ -3942,12 +3957,12 @@
         <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="G46" t="s">
         <v>172</v>
@@ -3965,12 +3980,12 @@
         <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="G47" t="s">
         <v>175</v>
@@ -3988,12 +4003,12 @@
         <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="G48" t="s">
         <v>175</v>
@@ -4011,12 +4026,12 @@
         <v>178</v>
       </c>
       <c r="B49" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
@@ -4034,7 +4049,7 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -4050,10 +4065,10 @@
         <v>182</v>
       </c>
       <c r="B51" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C51" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -4062,7 +4077,7 @@
         <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="G51" t="s">
         <v>185</v>
@@ -4080,10 +4095,10 @@
         <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C52" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D52" t="s">
         <v>188</v>
@@ -4092,7 +4107,7 @@
         <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="G52" t="s">
         <v>190</v>
@@ -4110,7 +4125,7 @@
         <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D53"/>
       <c r="E53"/>
@@ -4126,10 +4141,10 @@
         <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C54" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
@@ -4138,7 +4153,7 @@
         <v>195</v>
       </c>
       <c r="F54" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G54" t="s">
         <v>196</v>
@@ -4156,7 +4171,7 @@
         <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D55"/>
       <c r="E55"/>
@@ -4172,10 +4187,10 @@
         <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C56" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D56" t="s">
         <v>200</v>
@@ -4184,7 +4199,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -4202,10 +4217,10 @@
         <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C57" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D57" t="s">
         <v>205</v>
@@ -4214,7 +4229,7 @@
         <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="G57" t="s">
         <v>207</v>
@@ -4232,10 +4247,10 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C58" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D58" t="s">
         <v>210</v>
@@ -4244,7 +4259,7 @@
         <v>211</v>
       </c>
       <c r="F58" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G58" t="s">
         <v>212</v>
@@ -4262,10 +4277,10 @@
         <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C59" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D59" t="s">
         <v>215</v>
@@ -4274,7 +4289,7 @@
         <v>216</v>
       </c>
       <c r="F59" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="G59" t="s">
         <v>217</v>
@@ -4292,10 +4307,10 @@
         <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C60" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D60" t="s">
         <v>220</v>
@@ -4304,7 +4319,7 @@
         <v>221</v>
       </c>
       <c r="F60" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="G60" t="s">
         <v>222</v>
@@ -4322,10 +4337,10 @@
         <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C61" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="D61" t="s">
         <v>225</v>
@@ -4334,7 +4349,7 @@
         <v>226</v>
       </c>
       <c r="F61" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G61" t="s">
         <v>227</v>
@@ -4352,10 +4367,10 @@
         <v>229</v>
       </c>
       <c r="B62" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C62" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D62" t="s">
         <v>230</v>
@@ -4364,7 +4379,7 @@
         <v>231</v>
       </c>
       <c r="F62" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="G62" t="s">
         <v>232</v>
@@ -4382,10 +4397,10 @@
         <v>234</v>
       </c>
       <c r="B63" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C63" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D63" t="s">
         <v>235</v>
@@ -4394,7 +4409,7 @@
         <v>236</v>
       </c>
       <c r="F63" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="G63" t="s">
         <v>237</v>
@@ -4412,12 +4427,12 @@
         <v>239</v>
       </c>
       <c r="B64" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D64"/>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="G64" t="s">
         <v>240</v>
@@ -4435,12 +4450,12 @@
         <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D65"/>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="G65" t="s">
         <v>243</v>
@@ -4458,12 +4473,12 @@
         <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D66"/>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="G66" t="s">
         <v>246</v>
@@ -4481,12 +4496,12 @@
         <v>248</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="G67" t="s">
         <v>249</v>
@@ -4504,12 +4519,12 @@
         <v>251</v>
       </c>
       <c r="B68" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="G68" t="s">
         <v>252</v>
@@ -4527,12 +4542,12 @@
         <v>254</v>
       </c>
       <c r="B69" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G69" t="s">
         <v>255</v>
@@ -4550,12 +4565,12 @@
         <v>257</v>
       </c>
       <c r="B70" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="G70" t="s">
         <v>258</v>
@@ -4573,12 +4588,12 @@
         <v>260</v>
       </c>
       <c r="B71" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G71" t="s">
         <v>261</v>
@@ -4596,12 +4611,12 @@
         <v>263</v>
       </c>
       <c r="B72" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="G72" t="s">
         <v>264</v>
@@ -4619,7 +4634,7 @@
         <v>266</v>
       </c>
       <c r="B73" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D73"/>
       <c r="E73"/>
@@ -4637,7 +4652,7 @@
         <v>268</v>
       </c>
       <c r="B74" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D74"/>
       <c r="E74"/>
@@ -4655,10 +4670,10 @@
         <v>269</v>
       </c>
       <c r="B75" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C75" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D75" t="s">
         <v>270</v>
@@ -4667,7 +4682,7 @@
         <v>271</v>
       </c>
       <c r="F75" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="G75" t="s">
         <v>272</v>
@@ -4685,10 +4700,10 @@
         <v>274</v>
       </c>
       <c r="B76" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C76" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D76" t="s">
         <v>275</v>
@@ -4697,7 +4712,7 @@
         <v>276</v>
       </c>
       <c r="F76" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G76" t="s">
         <v>277</v>
@@ -4715,10 +4730,10 @@
         <v>279</v>
       </c>
       <c r="B77" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C77" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D77" t="s">
         <v>280</v>
@@ -4727,7 +4742,7 @@
         <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="G77" t="s">
         <v>282</v>
@@ -4745,10 +4760,10 @@
         <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C78" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D78" t="s">
         <v>285</v>
@@ -4757,7 +4772,7 @@
         <v>286</v>
       </c>
       <c r="F78" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="G78" t="s">
         <v>287</v>
@@ -4775,10 +4790,10 @@
         <v>289</v>
       </c>
       <c r="B79" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C79" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D79" t="s">
         <v>290</v>
@@ -4787,7 +4802,7 @@
         <v>291</v>
       </c>
       <c r="F79" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G79" t="s">
         <v>292</v>
@@ -4805,7 +4820,7 @@
         <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D80"/>
       <c r="E80"/>
@@ -4826,10 +4841,10 @@
         <v>296</v>
       </c>
       <c r="B81" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C81" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="D81" t="s">
         <v>297</v>
@@ -4838,7 +4853,7 @@
         <v>298</v>
       </c>
       <c r="F81" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="G81" t="s">
         <v>299</v>
@@ -4856,10 +4871,10 @@
         <v>301</v>
       </c>
       <c r="B82" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C82" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D82" t="s">
         <v>302</v>
@@ -4868,7 +4883,7 @@
         <v>303</v>
       </c>
       <c r="F82" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G82" t="s">
         <v>304</v>
@@ -4886,10 +4901,10 @@
         <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C83" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D83" t="s">
         <v>307</v>
@@ -4898,7 +4913,7 @@
         <v>308</v>
       </c>
       <c r="F83" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="G83" t="s">
         <v>309</v>
@@ -4916,10 +4931,10 @@
         <v>311</v>
       </c>
       <c r="B84" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C84" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D84" t="s">
         <v>312</v>
@@ -4928,7 +4943,7 @@
         <v>313</v>
       </c>
       <c r="F84" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="G84" t="s">
         <v>232</v>
@@ -4946,10 +4961,10 @@
         <v>314</v>
       </c>
       <c r="B85" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C85" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D85" t="s">
         <v>315</v>
@@ -4958,7 +4973,7 @@
         <v>316</v>
       </c>
       <c r="F85" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="G85" t="s">
         <v>317</v>
@@ -4976,10 +4991,10 @@
         <v>319</v>
       </c>
       <c r="B86" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C86" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D86" t="s">
         <v>320</v>
@@ -4988,7 +5003,7 @@
         <v>321</v>
       </c>
       <c r="F86" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="G86" t="s">
         <v>322</v>
@@ -5006,12 +5021,12 @@
         <v>324</v>
       </c>
       <c r="B87" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="G87" t="s">
         <v>325</v>
@@ -5029,12 +5044,12 @@
         <v>327</v>
       </c>
       <c r="B88" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="G88" t="s">
         <v>325</v>
@@ -5052,12 +5067,12 @@
         <v>328</v>
       </c>
       <c r="B89" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="G89" t="s">
         <v>325</v>
@@ -5075,12 +5090,12 @@
         <v>329</v>
       </c>
       <c r="B90" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="G90" t="s">
         <v>330</v>
@@ -5098,12 +5113,12 @@
         <v>332</v>
       </c>
       <c r="B91" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="G91" t="s">
         <v>333</v>
@@ -5121,12 +5136,12 @@
         <v>335</v>
       </c>
       <c r="B92" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="G92" t="s">
         <v>336</v>
@@ -5144,12 +5159,12 @@
         <v>338</v>
       </c>
       <c r="B93" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="G93" t="s">
         <v>339</v>
@@ -5167,10 +5182,10 @@
         <v>341</v>
       </c>
       <c r="B94" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C94" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D94" t="s">
         <v>342</v>
@@ -5179,7 +5194,7 @@
         <v>343</v>
       </c>
       <c r="F94" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="G94" t="s">
         <v>344</v>
@@ -5197,12 +5212,12 @@
         <v>346</v>
       </c>
       <c r="B95" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="G95" t="s">
         <v>347</v>
@@ -5220,12 +5235,12 @@
         <v>349</v>
       </c>
       <c r="B96" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G96" t="s">
         <v>350</v>
@@ -5243,12 +5258,12 @@
         <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="G97" t="s">
         <v>353</v>
@@ -5266,12 +5281,12 @@
         <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="G98" t="s">
         <v>356</v>
@@ -5289,12 +5304,12 @@
         <v>358</v>
       </c>
       <c r="B99" t="s">
-        <v>594</v>
+        <v>15</v>
       </c>
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="G99" t="s">
         <v>359</v>
@@ -5312,10 +5327,10 @@
         <v>361</v>
       </c>
       <c r="B100" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C100" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D100" t="s">
         <v>362</v>
@@ -5324,7 +5339,7 @@
         <v>363</v>
       </c>
       <c r="F100" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="G100" t="s">
         <v>364</v>
@@ -5342,10 +5357,10 @@
         <v>366</v>
       </c>
       <c r="B101" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C101" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D101" t="s">
         <v>367</v>
@@ -5354,7 +5369,7 @@
         <v>368</v>
       </c>
       <c r="F101" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G101" t="s">
         <v>277</v>
@@ -5372,10 +5387,10 @@
         <v>369</v>
       </c>
       <c r="B102" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C102" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D102" t="s">
         <v>367</v>
@@ -5384,7 +5399,7 @@
         <v>368</v>
       </c>
       <c r="F102" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G102" t="s">
         <v>277</v>
@@ -5402,10 +5417,10 @@
         <v>370</v>
       </c>
       <c r="B103" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C103" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D103" t="s">
         <v>371</v>
@@ -5414,7 +5429,7 @@
         <v>372</v>
       </c>
       <c r="F103" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="G103"/>
       <c r="H103" t="s">
@@ -5430,10 +5445,10 @@
         <v>374</v>
       </c>
       <c r="B104" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C104" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D104" t="s">
         <v>375</v>
@@ -5442,7 +5457,7 @@
         <v>376</v>
       </c>
       <c r="F104" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G104" t="s">
         <v>277</v>
@@ -5460,10 +5475,10 @@
         <v>377</v>
       </c>
       <c r="B105" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C105" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D105" t="s">
         <v>378</v>
@@ -5490,10 +5505,10 @@
         <v>381</v>
       </c>
       <c r="B106" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C106" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D106" t="s">
         <v>382</v>
@@ -5520,10 +5535,10 @@
         <v>384</v>
       </c>
       <c r="B107" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C107" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D107" t="s">
         <v>385</v>
@@ -5550,10 +5565,10 @@
         <v>387</v>
       </c>
       <c r="B108" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C108" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D108" t="s">
         <v>388</v>
@@ -5580,10 +5595,10 @@
         <v>390</v>
       </c>
       <c r="B109" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C109" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D109" t="s">
         <v>391</v>
@@ -5592,7 +5607,7 @@
         <v>392</v>
       </c>
       <c r="F109" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="G109" t="s">
         <v>393</v>
@@ -5610,12 +5625,12 @@
         <v>395</v>
       </c>
       <c r="B110" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D110"/>
       <c r="E110"/>
       <c r="F110" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="G110" t="s">
         <v>396</v>
@@ -5633,10 +5648,10 @@
         <v>398</v>
       </c>
       <c r="B111" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C111" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D111" t="s">
         <v>399</v>
@@ -5645,7 +5660,7 @@
         <v>400</v>
       </c>
       <c r="F111" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="G111" t="s">
         <v>401</v>
@@ -5663,10 +5678,10 @@
         <v>403</v>
       </c>
       <c r="B112" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C112" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D112" t="s">
         <v>404</v>
@@ -5675,7 +5690,7 @@
         <v>405</v>
       </c>
       <c r="F112" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="G112" t="s">
         <v>406</v>
@@ -5693,12 +5708,12 @@
         <v>408</v>
       </c>
       <c r="B113" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="G113" t="s">
         <v>409</v>
@@ -5716,10 +5731,10 @@
         <v>411</v>
       </c>
       <c r="B114" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C114" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="D114" t="s">
         <v>412</v>
@@ -5728,7 +5743,7 @@
         <v>413</v>
       </c>
       <c r="F114" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="G114" t="s">
         <v>414</v>
@@ -5746,10 +5761,10 @@
         <v>416</v>
       </c>
       <c r="B115" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C115" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D115" t="s">
         <v>417</v>
@@ -5758,7 +5773,7 @@
         <v>418</v>
       </c>
       <c r="F115" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="G115" t="s">
         <v>419</v>
@@ -5776,12 +5791,12 @@
         <v>421</v>
       </c>
       <c r="B116" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="G116" t="s">
         <v>422</v>
@@ -5799,10 +5814,10 @@
         <v>424</v>
       </c>
       <c r="B117" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C117" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D117" t="s">
         <v>425</v>
@@ -5811,7 +5826,7 @@
         <v>426</v>
       </c>
       <c r="F117" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="G117" t="s">
         <v>427</v>
@@ -5829,10 +5844,10 @@
         <v>429</v>
       </c>
       <c r="B118" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C118" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D118" t="s">
         <v>430</v>
@@ -5841,7 +5856,7 @@
         <v>431</v>
       </c>
       <c r="F118" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="G118" t="s">
         <v>432</v>
@@ -5859,12 +5874,12 @@
         <v>434</v>
       </c>
       <c r="B119" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D119"/>
       <c r="E119"/>
       <c r="F119" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="G119" t="s">
         <v>435</v>
@@ -5882,10 +5897,10 @@
         <v>437</v>
       </c>
       <c r="B120" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C120" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="D120" t="s">
         <v>438</v>
@@ -5894,7 +5909,7 @@
         <v>439</v>
       </c>
       <c r="F120" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="G120" t="s">
         <v>440</v>
@@ -5912,10 +5927,10 @@
         <v>442</v>
       </c>
       <c r="B121" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C121" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D121" t="s">
         <v>443</v>
@@ -5924,7 +5939,7 @@
         <v>444</v>
       </c>
       <c r="F121" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="G121" t="s">
         <v>445</v>
@@ -5942,10 +5957,10 @@
         <v>447</v>
       </c>
       <c r="B122" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C122" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="D122" t="s">
         <v>448</v>
@@ -5954,7 +5969,7 @@
         <v>449</v>
       </c>
       <c r="F122" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="G122" t="s">
         <v>450</v>
@@ -5972,10 +5987,10 @@
         <v>452</v>
       </c>
       <c r="B123" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C123" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="D123" t="s">
         <v>453</v>
@@ -5984,7 +5999,7 @@
         <v>454</v>
       </c>
       <c r="F123" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="G123" t="s">
         <v>455</v>
@@ -6002,10 +6017,10 @@
         <v>457</v>
       </c>
       <c r="B124" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C124" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D124" t="s">
         <v>458</v>
@@ -6014,7 +6029,7 @@
         <v>459</v>
       </c>
       <c r="F124" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="G124" t="s">
         <v>460</v>
@@ -6032,10 +6047,10 @@
         <v>462</v>
       </c>
       <c r="B125" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C125" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D125" t="s">
         <v>463</v>
@@ -6044,7 +6059,7 @@
         <v>464</v>
       </c>
       <c r="F125" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="G125" t="s">
         <v>465</v>
@@ -6062,10 +6077,10 @@
         <v>467</v>
       </c>
       <c r="B126" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C126" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D126" t="s">
         <v>468</v>
@@ -6074,7 +6089,7 @@
         <v>469</v>
       </c>
       <c r="F126" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="G126" t="s">
         <v>470</v>
@@ -6092,10 +6107,10 @@
         <v>472</v>
       </c>
       <c r="B127" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C127" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D127" t="s">
         <v>473</v>
@@ -6104,7 +6119,7 @@
         <v>474</v>
       </c>
       <c r="F127" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="G127" t="s">
         <v>475</v>
@@ -6122,10 +6137,10 @@
         <v>477</v>
       </c>
       <c r="B128" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C128" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="D128" t="s">
         <v>478</v>
@@ -6134,7 +6149,7 @@
         <v>479</v>
       </c>
       <c r="F128" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="G128" t="s">
         <v>480</v>
@@ -6152,10 +6167,10 @@
         <v>482</v>
       </c>
       <c r="B129" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C129" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D129" t="s">
         <v>483</v>
@@ -6164,7 +6179,7 @@
         <v>484</v>
       </c>
       <c r="F129" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="G129" t="s">
         <v>485</v>
@@ -6182,10 +6197,10 @@
         <v>487</v>
       </c>
       <c r="B130" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C130" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="D130" t="s">
         <v>488</v>
@@ -6194,7 +6209,7 @@
         <v>489</v>
       </c>
       <c r="F130" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="G130" t="s">
         <v>490</v>
@@ -6212,10 +6227,10 @@
         <v>492</v>
       </c>
       <c r="B131" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C131" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D131" t="s">
         <v>493</v>
@@ -6224,7 +6239,7 @@
         <v>494</v>
       </c>
       <c r="F131" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="G131" t="s">
         <v>495</v>
@@ -6242,10 +6257,10 @@
         <v>497</v>
       </c>
       <c r="B132" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C132" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D132" t="s">
         <v>498</v>
@@ -6254,7 +6269,7 @@
         <v>499</v>
       </c>
       <c r="F132" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="G132" t="s">
         <v>500</v>
@@ -6272,10 +6287,10 @@
         <v>502</v>
       </c>
       <c r="B133" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C133" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="D133" t="s">
         <v>503</v>
@@ -6284,7 +6299,7 @@
         <v>504</v>
       </c>
       <c r="F133" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="G133" t="s">
         <v>505</v>
@@ -6302,10 +6317,10 @@
         <v>507</v>
       </c>
       <c r="B134" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C134" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D134" t="s">
         <v>508</v>
@@ -6314,7 +6329,7 @@
         <v>509</v>
       </c>
       <c r="F134" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="G134" t="s">
         <v>510</v>
@@ -6332,10 +6347,10 @@
         <v>512</v>
       </c>
       <c r="B135" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C135" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D135" t="s">
         <v>513</v>
@@ -6344,7 +6359,7 @@
         <v>514</v>
       </c>
       <c r="F135" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="G135" t="s">
         <v>515</v>
@@ -6362,10 +6377,10 @@
         <v>517</v>
       </c>
       <c r="B136" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C136" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D136" t="s">
         <v>518</v>
@@ -6374,7 +6389,7 @@
         <v>519</v>
       </c>
       <c r="F136" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="G136" t="s">
         <v>520</v>
@@ -6392,10 +6407,10 @@
         <v>522</v>
       </c>
       <c r="B137" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C137" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="D137" t="s">
         <v>523</v>
@@ -6404,7 +6419,7 @@
         <v>524</v>
       </c>
       <c r="F137" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="G137" t="s">
         <v>525</v>
@@ -6422,10 +6437,10 @@
         <v>527</v>
       </c>
       <c r="B138" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C138" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D138" t="s">
         <v>528</v>
@@ -6434,7 +6449,7 @@
         <v>529</v>
       </c>
       <c r="F138" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="G138" t="s">
         <v>530</v>
@@ -6452,10 +6467,10 @@
         <v>532</v>
       </c>
       <c r="B139" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C139" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D139" t="s">
         <v>528</v>
@@ -6464,7 +6479,7 @@
         <v>529</v>
       </c>
       <c r="F139" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="G139" t="s">
         <v>530</v>
@@ -6482,10 +6497,10 @@
         <v>534</v>
       </c>
       <c r="B140" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C140" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="D140" t="s">
         <v>535</v>
@@ -6494,7 +6509,7 @@
         <v>536</v>
       </c>
       <c r="F140" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="G140" t="s">
         <v>537</v>
@@ -6512,10 +6527,10 @@
         <v>539</v>
       </c>
       <c r="B141" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C141" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D141" t="s">
         <v>540</v>
@@ -6524,7 +6539,7 @@
         <v>541</v>
       </c>
       <c r="F141" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="G141" t="s">
         <v>542</v>
@@ -6542,10 +6557,10 @@
         <v>544</v>
       </c>
       <c r="B142" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C142" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D142" t="s">
         <v>545</v>
@@ -6554,7 +6569,7 @@
         <v>546</v>
       </c>
       <c r="F142" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="G142" t="s">
         <v>547</v>
@@ -6572,10 +6587,10 @@
         <v>549</v>
       </c>
       <c r="B143" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C143" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D143" t="s">
         <v>550</v>
@@ -6584,7 +6599,7 @@
         <v>551</v>
       </c>
       <c r="F143" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="G143" t="s">
         <v>552</v>
@@ -6602,10 +6617,10 @@
         <v>554</v>
       </c>
       <c r="B144" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C144" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="D144" t="s">
         <v>555</v>
@@ -6614,7 +6629,7 @@
         <v>556</v>
       </c>
       <c r="F144" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="G144" t="s">
         <v>557</v>
@@ -6632,10 +6647,10 @@
         <v>559</v>
       </c>
       <c r="B145" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C145" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D145" t="s">
         <v>560</v>
@@ -6644,7 +6659,7 @@
         <v>561</v>
       </c>
       <c r="F145" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="G145" t="s">
         <v>562</v>
@@ -6662,10 +6677,10 @@
         <v>564</v>
       </c>
       <c r="B146" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C146" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="D146" t="s">
         <v>565</v>
@@ -6674,7 +6689,7 @@
         <v>566</v>
       </c>
       <c r="F146" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="G146" t="s">
         <v>567</v>
@@ -6692,10 +6707,10 @@
         <v>569</v>
       </c>
       <c r="B147" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C147" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -6704,7 +6719,7 @@
         <v>571</v>
       </c>
       <c r="F147" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="G147" t="s">
         <v>572</v>
@@ -6716,6 +6731,30 @@
       <c r="K147"/>
       <c r="M147"/>
       <c r="N147"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>574</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" t="s">
+        <v>575</v>
+      </c>
+      <c r="E148" t="s">
+        <v>576</v>
+      </c>
+      <c r="G148" t="s">
+        <v>577</v>
+      </c>
+      <c r="H148" t="s">
+        <v>578</v>
+      </c>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="M148"/>
+      <c r="N148"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:N2"/>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="818">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -778,10 +778,10 @@
     <t xml:space="preserve">vernis_gold5</t>
   </si>
   <si>
-    <t xml:space="preserve">The development of Vernis has begun. Grow the Hearth Stone in Vernis and report it to Loytel. Ask Loytel if you're unsure how to grow the Hearth Stone. Also, you need to continue conversations with your companions on the quest board. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ヴェルニースの開拓が始まった。ヴェルニースの盟約の石を成長させ、ロイテルに報告しなければならない。石の成長の方法がわからない場合は、ロイテルに相談しよう。また、依頼掲示板でクルイツゥア達との会話を進行させる必要がある。</t>
+    <t xml:space="preserve">The development of Vernis has begun. Grow the Hearth Stone in Vernis and report it to Loytel. Ask Loytel if you're unsure how to grow the Hearth Stone. Before reporting, you must progress your conversation events with your companions through the Quest Board.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヴェルニースの開拓が始まった。ヴェルニースの盟約の石を成長させ、ロイテルに報告しなければならない。石の成長の方法がわからない場合は、ロイテルに相談しよう。報告の前に、依頼掲示板からクルイツゥア達との会話を進行させておく必要がある。</t>
   </si>
   <si>
     <t xml:space="preserve">vernis_gold6</t>
@@ -4528,7 +4528,7 @@
         <v>251</v>
       </c>
       <c r="B68" t="s">
-        <v>593</v>
+        <v>15</v>
       </c>
       <c r="D68"/>
       <c r="E68"/>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="823">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
@@ -1118,6 +1118,21 @@
   </si>
   <si>
     <t xml:space="preserve">汝に魔術のたしなみはあるか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stone_dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nightly Routine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜の日課</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to finish up the books for tonight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さて、今夜も帳簿を片付けるとしよう。</t>
   </si>
   <si>
     <t xml:space="preserve">mokyu2</t>
@@ -1374,7 +1389,7 @@
   </si>
   <si>
     <t xml:space="preserve">Have you any plan to visit #3 by chance? I have my [qFriend] there I haven't seen in a long time. Can you deliver #2 for me?
-Have you heard the news? The #2 fever is gripping the town of #3 and people are boiling with enthusiasm! My [qFriend] is crying and begging me to send one. Can you goto #3 and deliver this package for me?
+Have you heard the news? The #2 fever is gripping the town of #3 and people are boiling with enthusiasm! My [qFriend] is crying and begging me to send one. Can you go to #3 and deliver this package for me?
 Please deliver #2 to #3. If you manage to deliver it safely, you shall recieve the payment.
 My [qFriend] has built a house in #3, so I'd like to send #2 as a celebratory gift. Could you deliver it for me?
 I don't know what it will be used for, but some [qClient] wants to purchase my #2. If you deliver it to #3, you will be paid #1.
@@ -1536,7 +1551,7 @@
     <t xml:space="preserve">defenseGame2</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster's den </t>
+    <t xml:space="preserve">Monster's den</t>
   </si>
   <si>
     <t xml:space="preserve">魔物の巣窟</t>
@@ -2869,10 +2884,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C3" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -2881,7 +2896,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -2899,10 +2914,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C4" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2911,7 +2926,7 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -2929,12 +2944,12 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -2952,10 +2967,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C6" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -2964,7 +2979,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -2982,10 +2997,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C7" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -2994,7 +3009,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G7" t="s">
         <v>36</v>
@@ -3012,12 +3027,12 @@
         <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="G8" t="s">
         <v>39</v>
@@ -3035,10 +3050,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C9" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -3047,7 +3062,7 @@
         <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="G9" t="s">
         <v>44</v>
@@ -3065,12 +3080,12 @@
         <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G10" t="s">
         <v>47</v>
@@ -3088,12 +3103,12 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="G11" t="s">
         <v>50</v>
@@ -3111,10 +3126,10 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C12" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -3123,7 +3138,7 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G12" t="s">
         <v>55</v>
@@ -3141,12 +3156,12 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -3164,10 +3179,10 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C14" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -3176,7 +3191,7 @@
         <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G14" t="s">
         <v>63</v>
@@ -3187,7 +3202,7 @@
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="M14" t="s">
         <v>65</v>
@@ -3201,10 +3216,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C15" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -3213,7 +3228,7 @@
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="G15" t="s">
         <v>70</v>
@@ -3238,10 +3253,10 @@
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C16" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -3250,7 +3265,7 @@
         <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
@@ -3268,10 +3283,10 @@
         <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C17" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D17" t="s">
         <v>80</v>
@@ -3280,7 +3295,7 @@
         <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G17" t="s">
         <v>82</v>
@@ -3298,10 +3313,10 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C18" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
@@ -3310,7 +3325,7 @@
         <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="G18" t="s">
         <v>87</v>
@@ -3328,10 +3343,10 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C19" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D19" t="s">
         <v>90</v>
@@ -3340,7 +3355,7 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G19"/>
       <c r="H19" t="s">
@@ -3356,12 +3371,12 @@
         <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="G20"/>
       <c r="H20" t="s">
@@ -3377,7 +3392,7 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -3393,10 +3408,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C22" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -3405,7 +3420,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -3423,7 +3438,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -3439,10 +3454,10 @@
         <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C24" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D24" t="s">
         <v>103</v>
@@ -3451,7 +3466,7 @@
         <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="G24" t="s">
         <v>105</v>
@@ -3469,12 +3484,12 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="G25" t="s">
         <v>108</v>
@@ -3492,12 +3507,12 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G26" t="s">
         <v>111</v>
@@ -3515,7 +3530,7 @@
         <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -3531,10 +3546,10 @@
         <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C28" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -3543,7 +3558,7 @@
         <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="G28" t="s">
         <v>117</v>
@@ -3561,7 +3576,7 @@
         <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -3577,10 +3592,10 @@
         <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C30" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -3589,7 +3604,7 @@
         <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G30" t="s">
         <v>82</v>
@@ -3607,10 +3622,10 @@
         <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C31" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="D31" t="s">
         <v>125</v>
@@ -3619,7 +3634,7 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G31" t="s">
         <v>82</v>
@@ -3637,10 +3652,10 @@
         <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C32" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D32" t="s">
         <v>128</v>
@@ -3649,7 +3664,7 @@
         <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="G32" t="s">
         <v>130</v>
@@ -3667,12 +3682,12 @@
         <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="G33" t="s">
         <v>133</v>
@@ -3690,7 +3705,7 @@
         <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D34"/>
       <c r="E34"/>
@@ -3706,10 +3721,10 @@
         <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C35" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D35" t="s">
         <v>137</v>
@@ -3718,7 +3733,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="G35" t="s">
         <v>139</v>
@@ -3736,12 +3751,12 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="G36" t="s">
         <v>142</v>
@@ -3759,12 +3774,12 @@
         <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="G37" t="s">
         <v>145</v>
@@ -3782,7 +3797,7 @@
         <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D38"/>
       <c r="E38"/>
@@ -3798,10 +3813,10 @@
         <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C39" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D39" t="s">
         <v>149</v>
@@ -3810,7 +3825,7 @@
         <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G39" t="s">
         <v>151</v>
@@ -3828,12 +3843,12 @@
         <v>153</v>
       </c>
       <c r="B40" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="G40" t="s">
         <v>154</v>
@@ -3851,7 +3866,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D41"/>
       <c r="E41"/>
@@ -3867,10 +3882,10 @@
         <v>157</v>
       </c>
       <c r="B42" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C42" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="D42" t="s">
         <v>158</v>
@@ -3879,7 +3894,7 @@
         <v>159</v>
       </c>
       <c r="F42" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="G42" t="s">
         <v>160</v>
@@ -3897,7 +3912,7 @@
         <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D43"/>
       <c r="E43"/>
@@ -3913,10 +3928,10 @@
         <v>163</v>
       </c>
       <c r="B44" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C44" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D44" t="s">
         <v>164</v>
@@ -3925,7 +3940,7 @@
         <v>165</v>
       </c>
       <c r="F44" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G44" t="s">
         <v>166</v>
@@ -3943,12 +3958,12 @@
         <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="G45" t="s">
         <v>169</v>
@@ -3966,12 +3981,12 @@
         <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="G46" t="s">
         <v>172</v>
@@ -3989,12 +4004,12 @@
         <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G47" t="s">
         <v>175</v>
@@ -4012,12 +4027,12 @@
         <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="G48" t="s">
         <v>175</v>
@@ -4035,12 +4050,12 @@
         <v>178</v>
       </c>
       <c r="B49" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
@@ -4058,7 +4073,7 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -4074,10 +4089,10 @@
         <v>182</v>
       </c>
       <c r="B51" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C51" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -4086,7 +4101,7 @@
         <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="G51" t="s">
         <v>185</v>
@@ -4104,10 +4119,10 @@
         <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C52" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D52" t="s">
         <v>188</v>
@@ -4116,7 +4131,7 @@
         <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G52" t="s">
         <v>190</v>
@@ -4134,7 +4149,7 @@
         <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D53"/>
       <c r="E53"/>
@@ -4150,10 +4165,10 @@
         <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C54" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
@@ -4162,7 +4177,7 @@
         <v>195</v>
       </c>
       <c r="F54" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="G54" t="s">
         <v>196</v>
@@ -4180,7 +4195,7 @@
         <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D55"/>
       <c r="E55"/>
@@ -4196,10 +4211,10 @@
         <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C56" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D56" t="s">
         <v>200</v>
@@ -4208,7 +4223,7 @@
         <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="G56" t="s">
         <v>202</v>
@@ -4226,10 +4241,10 @@
         <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C57" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D57" t="s">
         <v>205</v>
@@ -4238,7 +4253,7 @@
         <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="G57" t="s">
         <v>207</v>
@@ -4256,10 +4271,10 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C58" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D58" t="s">
         <v>210</v>
@@ -4268,7 +4283,7 @@
         <v>211</v>
       </c>
       <c r="F58" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="G58" t="s">
         <v>212</v>
@@ -4286,10 +4301,10 @@
         <v>214</v>
       </c>
       <c r="B59" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C59" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D59" t="s">
         <v>215</v>
@@ -4298,7 +4313,7 @@
         <v>216</v>
       </c>
       <c r="F59" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="G59" t="s">
         <v>217</v>
@@ -4316,10 +4331,10 @@
         <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C60" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D60" t="s">
         <v>220</v>
@@ -4328,7 +4343,7 @@
         <v>221</v>
       </c>
       <c r="F60" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="G60" t="s">
         <v>222</v>
@@ -4346,10 +4361,10 @@
         <v>224</v>
       </c>
       <c r="B61" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C61" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D61" t="s">
         <v>225</v>
@@ -4358,7 +4373,7 @@
         <v>226</v>
       </c>
       <c r="F61" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="G61" t="s">
         <v>227</v>
@@ -4376,10 +4391,10 @@
         <v>229</v>
       </c>
       <c r="B62" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C62" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D62" t="s">
         <v>230</v>
@@ -4388,7 +4403,7 @@
         <v>231</v>
       </c>
       <c r="F62" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G62" t="s">
         <v>232</v>
@@ -4406,10 +4421,10 @@
         <v>234</v>
       </c>
       <c r="B63" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C63" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="D63" t="s">
         <v>235</v>
@@ -4418,7 +4433,7 @@
         <v>236</v>
       </c>
       <c r="F63" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="G63" t="s">
         <v>237</v>
@@ -4436,12 +4451,12 @@
         <v>239</v>
       </c>
       <c r="B64" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D64"/>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G64" t="s">
         <v>240</v>
@@ -4459,12 +4474,12 @@
         <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D65"/>
       <c r="E65"/>
       <c r="F65" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="G65" t="s">
         <v>243</v>
@@ -4482,12 +4497,12 @@
         <v>245</v>
       </c>
       <c r="B66" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D66"/>
       <c r="E66"/>
       <c r="F66" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="G66" t="s">
         <v>246</v>
@@ -4505,12 +4520,12 @@
         <v>248</v>
       </c>
       <c r="B67" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G67" t="s">
         <v>249</v>
@@ -4528,12 +4543,12 @@
         <v>251</v>
       </c>
       <c r="B68" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="G68" t="s">
         <v>252</v>
@@ -4551,12 +4566,12 @@
         <v>254</v>
       </c>
       <c r="B69" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="G69" t="s">
         <v>255</v>
@@ -4574,12 +4589,12 @@
         <v>257</v>
       </c>
       <c r="B70" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G70" t="s">
         <v>258</v>
@@ -4597,12 +4612,12 @@
         <v>260</v>
       </c>
       <c r="B71" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="G71" t="s">
         <v>261</v>
@@ -4620,12 +4635,12 @@
         <v>263</v>
       </c>
       <c r="B72" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G72" t="s">
         <v>264</v>
@@ -4643,7 +4658,7 @@
         <v>266</v>
       </c>
       <c r="B73" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D73"/>
       <c r="E73"/>
@@ -4661,7 +4676,7 @@
         <v>268</v>
       </c>
       <c r="B74" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D74"/>
       <c r="E74"/>
@@ -4679,10 +4694,10 @@
         <v>269</v>
       </c>
       <c r="B75" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C75" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D75" t="s">
         <v>270</v>
@@ -4691,7 +4706,7 @@
         <v>271</v>
       </c>
       <c r="F75" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="G75" t="s">
         <v>272</v>
@@ -4709,10 +4724,10 @@
         <v>274</v>
       </c>
       <c r="B76" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C76" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D76" t="s">
         <v>275</v>
@@ -4721,7 +4736,7 @@
         <v>276</v>
       </c>
       <c r="F76" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="G76" t="s">
         <v>277</v>
@@ -4739,10 +4754,10 @@
         <v>279</v>
       </c>
       <c r="B77" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C77" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D77" t="s">
         <v>280</v>
@@ -4751,7 +4766,7 @@
         <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="G77" t="s">
         <v>282</v>
@@ -4769,10 +4784,10 @@
         <v>284</v>
       </c>
       <c r="B78" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C78" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D78" t="s">
         <v>285</v>
@@ -4781,7 +4796,7 @@
         <v>286</v>
       </c>
       <c r="F78" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="G78" t="s">
         <v>287</v>
@@ -4799,10 +4814,10 @@
         <v>289</v>
       </c>
       <c r="B79" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C79" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D79" t="s">
         <v>290</v>
@@ -4811,7 +4826,7 @@
         <v>291</v>
       </c>
       <c r="F79" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="G79" t="s">
         <v>292</v>
@@ -4829,7 +4844,7 @@
         <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D80"/>
       <c r="E80"/>
@@ -4850,10 +4865,10 @@
         <v>296</v>
       </c>
       <c r="B81" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C81" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D81" t="s">
         <v>297</v>
@@ -4862,7 +4877,7 @@
         <v>298</v>
       </c>
       <c r="F81" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="G81" t="s">
         <v>299</v>
@@ -4880,10 +4895,10 @@
         <v>301</v>
       </c>
       <c r="B82" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C82" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D82" t="s">
         <v>302</v>
@@ -4892,7 +4907,7 @@
         <v>303</v>
       </c>
       <c r="F82" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="G82" t="s">
         <v>304</v>
@@ -4910,10 +4925,10 @@
         <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C83" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D83" t="s">
         <v>307</v>
@@ -4922,7 +4937,7 @@
         <v>308</v>
       </c>
       <c r="F83" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="G83" t="s">
         <v>309</v>
@@ -4940,10 +4955,10 @@
         <v>311</v>
       </c>
       <c r="B84" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C84" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D84" t="s">
         <v>312</v>
@@ -4952,7 +4967,7 @@
         <v>313</v>
       </c>
       <c r="F84" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G84" t="s">
         <v>232</v>
@@ -4970,10 +4985,10 @@
         <v>314</v>
       </c>
       <c r="B85" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C85" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D85" t="s">
         <v>315</v>
@@ -4982,7 +4997,7 @@
         <v>316</v>
       </c>
       <c r="F85" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="G85" t="s">
         <v>317</v>
@@ -5000,10 +5015,10 @@
         <v>319</v>
       </c>
       <c r="B86" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C86" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D86" t="s">
         <v>320</v>
@@ -5012,7 +5027,7 @@
         <v>321</v>
       </c>
       <c r="F86" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="G86" t="s">
         <v>322</v>
@@ -5030,12 +5045,12 @@
         <v>324</v>
       </c>
       <c r="B87" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G87" t="s">
         <v>325</v>
@@ -5053,12 +5068,12 @@
         <v>327</v>
       </c>
       <c r="B88" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G88" t="s">
         <v>325</v>
@@ -5076,12 +5091,12 @@
         <v>328</v>
       </c>
       <c r="B89" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G89" t="s">
         <v>325</v>
@@ -5099,12 +5114,12 @@
         <v>329</v>
       </c>
       <c r="B90" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="G90" t="s">
         <v>330</v>
@@ -5122,12 +5137,12 @@
         <v>332</v>
       </c>
       <c r="B91" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="G91" t="s">
         <v>333</v>
@@ -5145,12 +5160,12 @@
         <v>335</v>
       </c>
       <c r="B92" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="G92" t="s">
         <v>336</v>
@@ -5168,12 +5183,12 @@
         <v>338</v>
       </c>
       <c r="B93" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="G93" t="s">
         <v>339</v>
@@ -5191,10 +5206,10 @@
         <v>341</v>
       </c>
       <c r="B94" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C94" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D94" t="s">
         <v>342</v>
@@ -5203,7 +5218,7 @@
         <v>343</v>
       </c>
       <c r="F94" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="G94" t="s">
         <v>344</v>
@@ -5221,12 +5236,12 @@
         <v>346</v>
       </c>
       <c r="B95" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="G95" t="s">
         <v>347</v>
@@ -5244,12 +5259,12 @@
         <v>349</v>
       </c>
       <c r="B96" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="G96" t="s">
         <v>350</v>
@@ -5267,12 +5282,12 @@
         <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="G97" t="s">
         <v>353</v>
@@ -5290,12 +5305,12 @@
         <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="G98" t="s">
         <v>356</v>
@@ -5313,12 +5328,12 @@
         <v>358</v>
       </c>
       <c r="B99" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="G99" t="s">
         <v>359</v>
@@ -5336,10 +5351,10 @@
         <v>361</v>
       </c>
       <c r="B100" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C100" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D100" t="s">
         <v>362</v>
@@ -5348,7 +5363,7 @@
         <v>363</v>
       </c>
       <c r="F100" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="G100" t="s">
         <v>364</v>
@@ -5366,10 +5381,7 @@
         <v>366</v>
       </c>
       <c r="B101" t="s">
-        <v>588</v>
-      </c>
-      <c r="C101" t="s">
-        <v>657</v>
+        <v>15</v>
       </c>
       <c r="D101" t="s">
         <v>367</v>
@@ -5377,14 +5389,11 @@
       <c r="E101" t="s">
         <v>368</v>
       </c>
-      <c r="F101" t="s">
-        <v>756</v>
-      </c>
       <c r="G101" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="H101" t="s">
-        <v>278</v>
+        <v>370</v>
       </c>
       <c r="J101"/>
       <c r="K101"/>
@@ -5393,22 +5402,22 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B102" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C102" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D102" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E102" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F102" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="G102" t="s">
         <v>277</v>
@@ -5423,26 +5432,28 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B103" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C103" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E103" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F103" t="s">
-        <v>777</v>
-      </c>
-      <c r="G103"/>
+        <v>761</v>
+      </c>
+      <c r="G103" t="s">
+        <v>277</v>
+      </c>
       <c r="H103" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="J103"/>
       <c r="K103"/>
@@ -5451,28 +5462,26 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B104" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="C104" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D104" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E104" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F104" t="s">
-        <v>756</v>
-      </c>
-      <c r="G104" t="s">
-        <v>277</v>
-      </c>
+        <v>782</v>
+      </c>
+      <c r="G104"/>
       <c r="H104" t="s">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="J104"/>
       <c r="K104"/>
@@ -5481,28 +5490,28 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B105" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C105" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D105" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E105" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F105" t="s">
-        <v>380</v>
+        <v>761</v>
       </c>
       <c r="G105" t="s">
-        <v>380</v>
+        <v>277</v>
       </c>
       <c r="H105" t="s">
-        <v>380</v>
+        <v>278</v>
       </c>
       <c r="J105"/>
       <c r="K105"/>
@@ -5511,28 +5520,28 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B106" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C106" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D106" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E106" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F106" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G106" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H106" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J106"/>
       <c r="K106"/>
@@ -5541,28 +5550,28 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B107" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C107" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D107" t="s">
+        <v>387</v>
+      </c>
+      <c r="E107" t="s">
+        <v>388</v>
+      </c>
+      <c r="F107" t="s">
         <v>385</v>
       </c>
-      <c r="E107" t="s">
-        <v>386</v>
-      </c>
-      <c r="F107" t="s">
-        <v>380</v>
-      </c>
       <c r="G107" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H107" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J107"/>
       <c r="K107"/>
@@ -5571,28 +5580,28 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B108" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C108" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D108" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E108" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F108" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G108" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H108" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J108"/>
       <c r="K108"/>
@@ -5601,28 +5610,28 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B109" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="C109" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D109" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E109" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F109" t="s">
-        <v>778</v>
+        <v>385</v>
       </c>
       <c r="G109" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="H109" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="J109"/>
       <c r="K109"/>
@@ -5634,18 +5643,25 @@
         <v>395</v>
       </c>
       <c r="B110" t="s">
-        <v>579</v>
-      </c>
-      <c r="D110"/>
-      <c r="E110"/>
+        <v>584</v>
+      </c>
+      <c r="C110" t="s">
+        <v>669</v>
+      </c>
+      <c r="D110" t="s">
+        <v>396</v>
+      </c>
+      <c r="E110" t="s">
+        <v>397</v>
+      </c>
       <c r="F110" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="G110" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H110" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J110"/>
       <c r="K110"/>
@@ -5654,22 +5670,15 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B111" t="s">
-        <v>588</v>
-      </c>
-      <c r="C111" t="s">
-        <v>665</v>
-      </c>
-      <c r="D111" t="s">
-        <v>399</v>
-      </c>
-      <c r="E111" t="s">
-        <v>400</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="D111"/>
+      <c r="E111"/>
       <c r="F111" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="G111" t="s">
         <v>401</v>
@@ -5687,10 +5696,10 @@
         <v>403</v>
       </c>
       <c r="B112" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C112" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D112" t="s">
         <v>404</v>
@@ -5699,7 +5708,7 @@
         <v>405</v>
       </c>
       <c r="F112" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="G112" t="s">
         <v>406</v>
@@ -5717,18 +5726,25 @@
         <v>408</v>
       </c>
       <c r="B113" t="s">
-        <v>579</v>
-      </c>
-      <c r="D113"/>
-      <c r="E113"/>
+        <v>584</v>
+      </c>
+      <c r="C113" t="s">
+        <v>671</v>
+      </c>
+      <c r="D113" t="s">
+        <v>409</v>
+      </c>
+      <c r="E113" t="s">
+        <v>410</v>
+      </c>
       <c r="F113" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="G113" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H113" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J113"/>
       <c r="K113"/>
@@ -5737,22 +5753,15 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B114" t="s">
-        <v>588</v>
-      </c>
-      <c r="C114" t="s">
-        <v>667</v>
-      </c>
-      <c r="D114" t="s">
-        <v>412</v>
-      </c>
-      <c r="E114" t="s">
-        <v>413</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="D114"/>
+      <c r="E114"/>
       <c r="F114" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="G114" t="s">
         <v>414</v>
@@ -5770,10 +5779,10 @@
         <v>416</v>
       </c>
       <c r="B115" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C115" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D115" t="s">
         <v>417</v>
@@ -5782,7 +5791,7 @@
         <v>418</v>
       </c>
       <c r="F115" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="G115" t="s">
         <v>419</v>
@@ -5800,18 +5809,25 @@
         <v>421</v>
       </c>
       <c r="B116" t="s">
-        <v>579</v>
-      </c>
-      <c r="D116"/>
-      <c r="E116"/>
+        <v>584</v>
+      </c>
+      <c r="C116" t="s">
+        <v>673</v>
+      </c>
+      <c r="D116" t="s">
+        <v>422</v>
+      </c>
+      <c r="E116" t="s">
+        <v>423</v>
+      </c>
       <c r="F116" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="G116" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H116" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J116"/>
       <c r="K116"/>
@@ -5820,22 +5836,15 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B117" t="s">
-        <v>588</v>
-      </c>
-      <c r="C117" t="s">
-        <v>669</v>
-      </c>
-      <c r="D117" t="s">
-        <v>425</v>
-      </c>
-      <c r="E117" t="s">
-        <v>426</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="D117"/>
+      <c r="E117"/>
       <c r="F117" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="G117" t="s">
         <v>427</v>
@@ -5853,10 +5862,10 @@
         <v>429</v>
       </c>
       <c r="B118" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="C118" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D118" t="s">
         <v>430</v>
@@ -5865,7 +5874,7 @@
         <v>431</v>
       </c>
       <c r="F118" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="G118" t="s">
         <v>432</v>
@@ -5883,18 +5892,25 @@
         <v>434</v>
       </c>
       <c r="B119" t="s">
-        <v>607</v>
-      </c>
-      <c r="D119"/>
-      <c r="E119"/>
+        <v>611</v>
+      </c>
+      <c r="C119" t="s">
+        <v>675</v>
+      </c>
+      <c r="D119" t="s">
+        <v>435</v>
+      </c>
+      <c r="E119" t="s">
+        <v>436</v>
+      </c>
       <c r="F119" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="G119" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H119" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J119"/>
       <c r="K119"/>
@@ -5903,22 +5919,15 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B120" t="s">
-        <v>588</v>
-      </c>
-      <c r="C120" t="s">
-        <v>671</v>
-      </c>
-      <c r="D120" t="s">
-        <v>438</v>
-      </c>
-      <c r="E120" t="s">
-        <v>439</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="D120"/>
+      <c r="E120"/>
       <c r="F120" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="G120" t="s">
         <v>440</v>
@@ -5936,10 +5945,10 @@
         <v>442</v>
       </c>
       <c r="B121" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C121" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D121" t="s">
         <v>443</v>
@@ -5948,7 +5957,7 @@
         <v>444</v>
       </c>
       <c r="F121" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="G121" t="s">
         <v>445</v>
@@ -5966,10 +5975,10 @@
         <v>447</v>
       </c>
       <c r="B122" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C122" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D122" t="s">
         <v>448</v>
@@ -5978,7 +5987,7 @@
         <v>449</v>
       </c>
       <c r="F122" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="G122" t="s">
         <v>450</v>
@@ -5996,10 +6005,10 @@
         <v>452</v>
       </c>
       <c r="B123" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="C123" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D123" t="s">
         <v>453</v>
@@ -6008,7 +6017,7 @@
         <v>454</v>
       </c>
       <c r="F123" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="G123" t="s">
         <v>455</v>
@@ -6026,10 +6035,10 @@
         <v>457</v>
       </c>
       <c r="B124" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C124" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D124" t="s">
         <v>458</v>
@@ -6038,7 +6047,7 @@
         <v>459</v>
       </c>
       <c r="F124" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="G124" t="s">
         <v>460</v>
@@ -6056,10 +6065,10 @@
         <v>462</v>
       </c>
       <c r="B125" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="C125" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D125" t="s">
         <v>463</v>
@@ -6068,7 +6077,7 @@
         <v>464</v>
       </c>
       <c r="F125" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="G125" t="s">
         <v>465</v>
@@ -6086,10 +6095,10 @@
         <v>467</v>
       </c>
       <c r="B126" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C126" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D126" t="s">
         <v>468</v>
@@ -6098,7 +6107,7 @@
         <v>469</v>
       </c>
       <c r="F126" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="G126" t="s">
         <v>470</v>
@@ -6116,10 +6125,10 @@
         <v>472</v>
       </c>
       <c r="B127" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="C127" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D127" t="s">
         <v>473</v>
@@ -6128,7 +6137,7 @@
         <v>474</v>
       </c>
       <c r="F127" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="G127" t="s">
         <v>475</v>
@@ -6146,10 +6155,10 @@
         <v>477</v>
       </c>
       <c r="B128" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C128" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D128" t="s">
         <v>478</v>
@@ -6158,7 +6167,7 @@
         <v>479</v>
       </c>
       <c r="F128" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="G128" t="s">
         <v>480</v>
@@ -6176,10 +6185,10 @@
         <v>482</v>
       </c>
       <c r="B129" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C129" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D129" t="s">
         <v>483</v>
@@ -6188,7 +6197,7 @@
         <v>484</v>
       </c>
       <c r="F129" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="G129" t="s">
         <v>485</v>
@@ -6206,10 +6215,10 @@
         <v>487</v>
       </c>
       <c r="B130" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C130" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D130" t="s">
         <v>488</v>
@@ -6218,7 +6227,7 @@
         <v>489</v>
       </c>
       <c r="F130" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="G130" t="s">
         <v>490</v>
@@ -6236,10 +6245,10 @@
         <v>492</v>
       </c>
       <c r="B131" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C131" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D131" t="s">
         <v>493</v>
@@ -6248,7 +6257,7 @@
         <v>494</v>
       </c>
       <c r="F131" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="G131" t="s">
         <v>495</v>
@@ -6266,10 +6275,10 @@
         <v>497</v>
       </c>
       <c r="B132" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C132" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D132" t="s">
         <v>498</v>
@@ -6278,7 +6287,7 @@
         <v>499</v>
       </c>
       <c r="F132" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="G132" t="s">
         <v>500</v>
@@ -6296,10 +6305,10 @@
         <v>502</v>
       </c>
       <c r="B133" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C133" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D133" t="s">
         <v>503</v>
@@ -6308,7 +6317,7 @@
         <v>504</v>
       </c>
       <c r="F133" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G133" t="s">
         <v>505</v>
@@ -6326,10 +6335,10 @@
         <v>507</v>
       </c>
       <c r="B134" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C134" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D134" t="s">
         <v>508</v>
@@ -6338,7 +6347,7 @@
         <v>509</v>
       </c>
       <c r="F134" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="G134" t="s">
         <v>510</v>
@@ -6356,10 +6365,10 @@
         <v>512</v>
       </c>
       <c r="B135" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C135" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D135" t="s">
         <v>513</v>
@@ -6368,7 +6377,7 @@
         <v>514</v>
       </c>
       <c r="F135" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="G135" t="s">
         <v>515</v>
@@ -6386,10 +6395,10 @@
         <v>517</v>
       </c>
       <c r="B136" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C136" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D136" t="s">
         <v>518</v>
@@ -6398,7 +6407,7 @@
         <v>519</v>
       </c>
       <c r="F136" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="G136" t="s">
         <v>520</v>
@@ -6416,10 +6425,10 @@
         <v>522</v>
       </c>
       <c r="B137" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C137" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D137" t="s">
         <v>523</v>
@@ -6428,7 +6437,7 @@
         <v>524</v>
       </c>
       <c r="F137" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G137" t="s">
         <v>525</v>
@@ -6446,10 +6455,10 @@
         <v>527</v>
       </c>
       <c r="B138" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C138" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D138" t="s">
         <v>528</v>
@@ -6458,7 +6467,7 @@
         <v>529</v>
       </c>
       <c r="F138" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="G138" t="s">
         <v>530</v>
@@ -6476,25 +6485,25 @@
         <v>532</v>
       </c>
       <c r="B139" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C139" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D139" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E139" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F139" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="G139" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H139" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
@@ -6503,25 +6512,25 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>537</v>
+      </c>
+      <c r="B140" t="s">
+        <v>593</v>
+      </c>
+      <c r="C140" t="s">
+        <v>694</v>
+      </c>
+      <c r="D140" t="s">
+        <v>533</v>
+      </c>
+      <c r="E140" t="s">
         <v>534</v>
       </c>
-      <c r="B140" t="s">
-        <v>588</v>
-      </c>
-      <c r="C140" t="s">
-        <v>690</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="F140" t="s">
+        <v>812</v>
+      </c>
+      <c r="G140" t="s">
         <v>535</v>
-      </c>
-      <c r="E140" t="s">
-        <v>536</v>
-      </c>
-      <c r="F140" t="s">
-        <v>808</v>
-      </c>
-      <c r="G140" t="s">
-        <v>537</v>
       </c>
       <c r="H140" t="s">
         <v>538</v>
@@ -6536,10 +6545,10 @@
         <v>539</v>
       </c>
       <c r="B141" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C141" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D141" t="s">
         <v>540</v>
@@ -6548,7 +6557,7 @@
         <v>541</v>
       </c>
       <c r="F141" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="G141" t="s">
         <v>542</v>
@@ -6566,10 +6575,10 @@
         <v>544</v>
       </c>
       <c r="B142" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C142" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D142" t="s">
         <v>545</v>
@@ -6578,7 +6587,7 @@
         <v>546</v>
       </c>
       <c r="F142" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="G142" t="s">
         <v>547</v>
@@ -6596,10 +6605,10 @@
         <v>549</v>
       </c>
       <c r="B143" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C143" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D143" t="s">
         <v>550</v>
@@ -6608,7 +6617,7 @@
         <v>551</v>
       </c>
       <c r="F143" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="G143" t="s">
         <v>552</v>
@@ -6626,10 +6635,10 @@
         <v>554</v>
       </c>
       <c r="B144" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C144" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D144" t="s">
         <v>555</v>
@@ -6638,7 +6647,7 @@
         <v>556</v>
       </c>
       <c r="F144" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="G144" t="s">
         <v>557</v>
@@ -6656,10 +6665,10 @@
         <v>559</v>
       </c>
       <c r="B145" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C145" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D145" t="s">
         <v>560</v>
@@ -6668,7 +6677,7 @@
         <v>561</v>
       </c>
       <c r="F145" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="G145" t="s">
         <v>562</v>
@@ -6686,10 +6695,10 @@
         <v>564</v>
       </c>
       <c r="B146" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="C146" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D146" t="s">
         <v>565</v>
@@ -6698,7 +6707,7 @@
         <v>566</v>
       </c>
       <c r="F146" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="G146" t="s">
         <v>567</v>
@@ -6716,10 +6725,10 @@
         <v>569</v>
       </c>
       <c r="B147" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C147" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D147" t="s">
         <v>570</v>
@@ -6728,7 +6737,7 @@
         <v>571</v>
       </c>
       <c r="F147" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="G147" t="s">
         <v>572</v>
@@ -6746,10 +6755,10 @@
         <v>574</v>
       </c>
       <c r="B148" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C148" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D148" t="s">
         <v>575</v>
@@ -6758,7 +6767,7 @@
         <v>576</v>
       </c>
       <c r="F148" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="G148" t="s">
         <v>577</v>
@@ -6770,6 +6779,36 @@
       <c r="K148"/>
       <c r="M148"/>
       <c r="N148"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>579</v>
+      </c>
+      <c r="B149" t="s">
+        <v>608</v>
+      </c>
+      <c r="C149" t="s">
+        <v>703</v>
+      </c>
+      <c r="D149" t="s">
+        <v>580</v>
+      </c>
+      <c r="E149" t="s">
+        <v>581</v>
+      </c>
+      <c r="F149" t="s">
+        <v>821</v>
+      </c>
+      <c r="G149" t="s">
+        <v>582</v>
+      </c>
+      <c r="H149" t="s">
+        <v>583</v>
+      </c>
+      <c r="J149"/>
+      <c r="K149"/>
+      <c r="M149"/>
+      <c r="N149"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:N2"/>
